--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_air_transport.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_air_transport.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08592334985935821</v>
+        <v>0.08574229148470981</v>
       </c>
       <c r="C2">
-        <v>4365.080221100937</v>
+        <v>4333.750148874185</v>
       </c>
       <c r="D2">
-        <v>3020.280221100937</v>
+        <v>3033.971148874185</v>
       </c>
       <c r="E2">
-        <v>-588.8</v>
+        <v>-543.779</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>45.02100000000001</v>
       </c>
       <c r="G2">
         <v>1344.8</v>
@@ -1445,28 +1445,28 @@
         <v>304.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.2645563</v>
       </c>
       <c r="N2">
-        <v>304.6</v>
+        <v>302.3354437</v>
       </c>
       <c r="O2">
-        <v>76.15000000000001</v>
+        <v>75.58386092500001</v>
       </c>
       <c r="P2">
-        <v>228.45</v>
+        <v>226.751582775</v>
       </c>
       <c r="Q2">
-        <v>347.65</v>
+        <v>345.951582775</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08592334985935821</v>
+        <v>0.08622731463102001</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8103113482567638</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.5075854373769</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08574229148470981</v>
+        <v>0.08556123311006142</v>
       </c>
       <c r="C3">
-        <v>4333.750148874185</v>
+        <v>4302.544763782927</v>
       </c>
       <c r="D3">
-        <v>3033.971148874185</v>
+        <v>3047.786763782927</v>
       </c>
       <c r="E3">
-        <v>-543.779</v>
+        <v>-498.7579999999999</v>
       </c>
       <c r="F3">
-        <v>45.02100000000001</v>
+        <v>90.04200000000002</v>
       </c>
       <c r="G3">
         <v>1344.8</v>
@@ -1527,28 +1527,28 @@
         <v>304.6</v>
       </c>
       <c r="M3">
-        <v>2.2645563</v>
+        <v>4.5291126</v>
       </c>
       <c r="N3">
-        <v>302.3354437</v>
+        <v>300.0708874</v>
       </c>
       <c r="O3">
-        <v>75.58386092500001</v>
+        <v>75.01772185</v>
       </c>
       <c r="P3">
-        <v>226.751582775</v>
+        <v>225.05316555</v>
       </c>
       <c r="Q3">
-        <v>345.951582775</v>
+        <v>344.25316555</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08622731463102001</v>
+        <v>0.0865374827653688</v>
       </c>
       <c r="T3">
-        <v>0.8103113482567638</v>
+        <v>0.8165282528774234</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.5075854373769</v>
+        <v>67.25379271868842</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08556123311006142</v>
+        <v>0.08538017473541301</v>
       </c>
       <c r="C4">
-        <v>4302.544763782927</v>
+        <v>4271.46577696034</v>
       </c>
       <c r="D4">
-        <v>3047.786763782927</v>
+        <v>3061.72877696034</v>
       </c>
       <c r="E4">
-        <v>-498.7579999999999</v>
+        <v>-453.737</v>
       </c>
       <c r="F4">
-        <v>90.04200000000002</v>
+        <v>135.063</v>
       </c>
       <c r="G4">
         <v>1344.8</v>
@@ -1609,28 +1609,28 @@
         <v>304.6</v>
       </c>
       <c r="M4">
-        <v>4.5291126</v>
+        <v>6.7936689</v>
       </c>
       <c r="N4">
-        <v>300.0708874</v>
+        <v>297.8063311</v>
       </c>
       <c r="O4">
-        <v>75.01772185</v>
+        <v>74.45158277500001</v>
       </c>
       <c r="P4">
-        <v>225.05316555</v>
+        <v>223.354748325</v>
       </c>
       <c r="Q4">
-        <v>344.25316555</v>
+        <v>342.554748325</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0865374827653688</v>
+        <v>0.08685404611898248</v>
       </c>
       <c r="T4">
-        <v>0.8165282528774234</v>
+        <v>0.8228733410985087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.25379271868842</v>
+        <v>44.83586181245895</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08538017473541301</v>
+        <v>0.08519911636076462</v>
       </c>
       <c r="C5">
-        <v>4271.46577696034</v>
+        <v>4240.51493099361</v>
       </c>
       <c r="D5">
-        <v>3061.72877696034</v>
+        <v>3075.798930993609</v>
       </c>
       <c r="E5">
-        <v>-453.737</v>
+        <v>-408.7159999999999</v>
       </c>
       <c r="F5">
-        <v>135.063</v>
+        <v>180.084</v>
       </c>
       <c r="G5">
         <v>1344.8</v>
@@ -1691,28 +1691,28 @@
         <v>304.6</v>
       </c>
       <c r="M5">
-        <v>6.7936689</v>
+        <v>9.058225200000001</v>
       </c>
       <c r="N5">
-        <v>297.8063311</v>
+        <v>295.5417748</v>
       </c>
       <c r="O5">
-        <v>74.45158277500001</v>
+        <v>73.88544370000001</v>
       </c>
       <c r="P5">
-        <v>223.354748325</v>
+        <v>221.6563311</v>
       </c>
       <c r="Q5">
-        <v>342.554748325</v>
+        <v>340.8563311</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08685404611898248</v>
+        <v>0.08717720454246315</v>
       </c>
       <c r="T5">
-        <v>0.8228733410985087</v>
+        <v>0.8293506186575337</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.83586181245895</v>
+        <v>33.62689635934422</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08519911636076462</v>
+        <v>0.08501805798611622</v>
       </c>
       <c r="C6">
-        <v>4240.51493099361</v>
+        <v>4209.694000649994</v>
       </c>
       <c r="D6">
-        <v>3075.798930993609</v>
+        <v>3089.999000649993</v>
       </c>
       <c r="E6">
-        <v>-408.7159999999999</v>
+        <v>-363.6949999999999</v>
       </c>
       <c r="F6">
-        <v>180.084</v>
+        <v>225.105</v>
       </c>
       <c r="G6">
         <v>1344.8</v>
@@ -1773,28 +1773,28 @@
         <v>304.6</v>
       </c>
       <c r="M6">
-        <v>9.058225200000001</v>
+        <v>11.3227815</v>
       </c>
       <c r="N6">
-        <v>295.5417748</v>
+        <v>293.2772185</v>
       </c>
       <c r="O6">
-        <v>73.88544370000001</v>
+        <v>73.319304625</v>
       </c>
       <c r="P6">
-        <v>221.6563311</v>
+        <v>219.957913875</v>
       </c>
       <c r="Q6">
-        <v>340.8563311</v>
+        <v>339.157913875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08717720454246315</v>
+        <v>0.08750716630117497</v>
       </c>
       <c r="T6">
-        <v>0.8293506186575337</v>
+        <v>0.8359642599546432</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.62689635934422</v>
+        <v>26.90151708747537</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08501805798611622</v>
+        <v>0.08483699961146783</v>
       </c>
       <c r="C7">
-        <v>4209.694000649994</v>
+        <v>4179.004793623101</v>
       </c>
       <c r="D7">
-        <v>3089.999000649993</v>
+        <v>3104.330793623101</v>
       </c>
       <c r="E7">
-        <v>-363.6949999999999</v>
+        <v>-318.6739999999999</v>
       </c>
       <c r="F7">
-        <v>225.105</v>
+        <v>270.126</v>
       </c>
       <c r="G7">
         <v>1344.8</v>
@@ -1855,28 +1855,28 @@
         <v>304.6</v>
       </c>
       <c r="M7">
-        <v>11.3227815</v>
+        <v>13.5873378</v>
       </c>
       <c r="N7">
-        <v>293.2772185</v>
+        <v>291.0126622</v>
       </c>
       <c r="O7">
-        <v>73.319304625</v>
+        <v>72.75316555000001</v>
       </c>
       <c r="P7">
-        <v>219.957913875</v>
+        <v>218.25949665</v>
       </c>
       <c r="Q7">
-        <v>339.157913875</v>
+        <v>337.45949665</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08750716630117497</v>
+        <v>0.08784414852283812</v>
       </c>
       <c r="T7">
-        <v>0.8359642599546432</v>
+        <v>0.8427186170240316</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.90151708747537</v>
+        <v>22.41793090622948</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08483699961146783</v>
+        <v>0.08465594123681944</v>
       </c>
       <c r="C8">
-        <v>4179.004793623101</v>
+        <v>4148.449151300031</v>
       </c>
       <c r="D8">
-        <v>3104.330793623101</v>
+        <v>3118.796151300031</v>
       </c>
       <c r="E8">
-        <v>-318.6739999999999</v>
+        <v>-273.653</v>
       </c>
       <c r="F8">
-        <v>270.126</v>
+        <v>315.147</v>
       </c>
       <c r="G8">
         <v>1344.8</v>
@@ -1937,28 +1937,28 @@
         <v>304.6</v>
       </c>
       <c r="M8">
-        <v>13.5873378</v>
+        <v>15.8518941</v>
       </c>
       <c r="N8">
-        <v>291.0126622</v>
+        <v>288.7481059</v>
       </c>
       <c r="O8">
-        <v>72.75316555000001</v>
+        <v>72.18702647500001</v>
       </c>
       <c r="P8">
-        <v>218.25949665</v>
+        <v>216.561079425</v>
       </c>
       <c r="Q8">
-        <v>337.45949665</v>
+        <v>335.761079425</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08784414852283812</v>
+        <v>0.0881883776739994</v>
       </c>
       <c r="T8">
-        <v>0.8427186170240316</v>
+        <v>0.8496182290841595</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.41793090622948</v>
+        <v>19.2153693481967</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08465594123681942</v>
+        <v>0.08447488286217106</v>
       </c>
       <c r="C9">
-        <v>4148.449151300032</v>
+        <v>4118.028949550059</v>
       </c>
       <c r="D9">
-        <v>3118.796151300032</v>
+        <v>3133.396949550059</v>
       </c>
       <c r="E9">
-        <v>-273.6529999999999</v>
+        <v>-228.6319999999999</v>
       </c>
       <c r="F9">
-        <v>315.147</v>
+        <v>360.1680000000001</v>
       </c>
       <c r="G9">
         <v>1344.8</v>
@@ -2019,28 +2019,28 @@
         <v>304.6</v>
       </c>
       <c r="M9">
-        <v>15.8518941</v>
+        <v>18.1164504</v>
       </c>
       <c r="N9">
-        <v>288.7481059</v>
+        <v>286.4835496</v>
       </c>
       <c r="O9">
-        <v>72.18702647500001</v>
+        <v>71.6208874</v>
       </c>
       <c r="P9">
-        <v>216.561079425</v>
+        <v>214.8626622</v>
       </c>
       <c r="Q9">
-        <v>335.761079425</v>
+        <v>334.0626622</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0881883776739994</v>
+        <v>0.08854009006757722</v>
       </c>
       <c r="T9">
-        <v>0.8496182290841595</v>
+        <v>0.8566678327108121</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.2153693481967</v>
+        <v>16.81344817967211</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08447488286217106</v>
+        <v>0.08429382448752265</v>
       </c>
       <c r="C10">
-        <v>4118.028949550059</v>
+        <v>4087.74609953559</v>
       </c>
       <c r="D10">
-        <v>3133.396949550059</v>
+        <v>3148.13509953559</v>
       </c>
       <c r="E10">
-        <v>-228.6319999999999</v>
+        <v>-183.6109999999999</v>
       </c>
       <c r="F10">
-        <v>360.1680000000001</v>
+        <v>405.189</v>
       </c>
       <c r="G10">
         <v>1344.8</v>
@@ -2101,28 +2101,28 @@
         <v>304.6</v>
       </c>
       <c r="M10">
-        <v>18.1164504</v>
+        <v>20.3810067</v>
       </c>
       <c r="N10">
-        <v>286.4835496</v>
+        <v>284.2189933</v>
       </c>
       <c r="O10">
-        <v>71.6208874</v>
+        <v>71.05474832500001</v>
       </c>
       <c r="P10">
-        <v>214.8626622</v>
+        <v>213.164244975</v>
       </c>
       <c r="Q10">
-        <v>334.0626622</v>
+        <v>332.364244975</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08854009006757722</v>
+        <v>0.08889953240387104</v>
       </c>
       <c r="T10">
-        <v>0.8566678327108121</v>
+        <v>0.8638723726809074</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.81344817967211</v>
+        <v>14.94528727081965</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08429382448752265</v>
+        <v>0.08411276611287426</v>
       </c>
       <c r="C11">
-        <v>4087.74609953559</v>
+        <v>4057.60254854609</v>
       </c>
       <c r="D11">
-        <v>3148.13509953559</v>
+        <v>3163.012548546089</v>
       </c>
       <c r="E11">
-        <v>-183.6109999999999</v>
+        <v>-138.59</v>
       </c>
       <c r="F11">
-        <v>405.189</v>
+        <v>450.21</v>
       </c>
       <c r="G11">
         <v>1344.8</v>
@@ -2183,28 +2183,28 @@
         <v>304.6</v>
       </c>
       <c r="M11">
-        <v>20.3810067</v>
+        <v>22.645563</v>
       </c>
       <c r="N11">
-        <v>284.2189933</v>
+        <v>281.954437</v>
       </c>
       <c r="O11">
-        <v>71.05474832500001</v>
+        <v>70.48860925000001</v>
       </c>
       <c r="P11">
-        <v>213.164244975</v>
+        <v>211.46582775</v>
       </c>
       <c r="Q11">
-        <v>332.364244975</v>
+        <v>330.66582775</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08889953240387104</v>
+        <v>0.08926696234763806</v>
       </c>
       <c r="T11">
-        <v>0.8638723726809074</v>
+        <v>0.8712370135392272</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.94528727081965</v>
+        <v>13.45075854373769</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08411276611287426</v>
+        <v>0.08405545773822586</v>
       </c>
       <c r="C12">
-        <v>4057.60254854609</v>
+        <v>4017.319881815816</v>
       </c>
       <c r="D12">
-        <v>3163.012548546089</v>
+        <v>3167.750881815816</v>
       </c>
       <c r="E12">
-        <v>-138.5899999999999</v>
+        <v>-93.5689999999999</v>
       </c>
       <c r="F12">
-        <v>450.21</v>
+        <v>495.2310000000001</v>
       </c>
       <c r="G12">
         <v>1344.8</v>
@@ -2265,45 +2265,45 @@
         <v>304.6</v>
       </c>
       <c r="M12">
-        <v>22.645563</v>
+        <v>25.6529658</v>
       </c>
       <c r="N12">
-        <v>281.954437</v>
+        <v>278.9470342</v>
       </c>
       <c r="O12">
-        <v>70.48860925000001</v>
+        <v>69.73675855</v>
       </c>
       <c r="P12">
-        <v>211.46582775</v>
+        <v>209.21027565</v>
       </c>
       <c r="Q12">
-        <v>330.66582775</v>
+        <v>328.41027565</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08926696234763806</v>
+        <v>0.08964264914407399</v>
       </c>
       <c r="T12">
-        <v>0.8712370135392272</v>
+        <v>0.8787671519449251</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.45075854373769</v>
+        <v>11.87387073973334</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08405545773822586</v>
+        <v>0.08388564936357747</v>
       </c>
       <c r="C13">
-        <v>4017.319881815816</v>
+        <v>3986.422590811745</v>
       </c>
       <c r="D13">
-        <v>3167.750881815816</v>
+        <v>3181.874590811744</v>
       </c>
       <c r="E13">
-        <v>-93.5689999999999</v>
+        <v>-48.54799999999989</v>
       </c>
       <c r="F13">
-        <v>495.2310000000001</v>
+        <v>540.2520000000001</v>
       </c>
       <c r="G13">
         <v>1344.8</v>
@@ -2347,28 +2347,28 @@
         <v>304.6</v>
       </c>
       <c r="M13">
-        <v>25.6529658</v>
+        <v>27.9850536</v>
       </c>
       <c r="N13">
-        <v>278.9470342</v>
+        <v>276.6149464</v>
       </c>
       <c r="O13">
-        <v>69.73675855</v>
+        <v>69.1537366</v>
       </c>
       <c r="P13">
-        <v>209.21027565</v>
+        <v>207.4612098</v>
       </c>
       <c r="Q13">
-        <v>328.41027565</v>
+        <v>326.6612098</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08964264914407399</v>
+        <v>0.09002687427679257</v>
       </c>
       <c r="T13">
-        <v>0.8787671519449251</v>
+        <v>0.8864684298598431</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.87387073973334</v>
+        <v>10.88438151142222</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08388564936357747</v>
+        <v>0.08371584098892906</v>
       </c>
       <c r="C14">
-        <v>3986.422590811745</v>
+        <v>3955.651807568338</v>
       </c>
       <c r="D14">
-        <v>3181.874590811744</v>
+        <v>3196.124807568338</v>
       </c>
       <c r="E14">
-        <v>-48.54799999999989</v>
+        <v>-3.52699999999993</v>
       </c>
       <c r="F14">
-        <v>540.2520000000001</v>
+        <v>585.273</v>
       </c>
       <c r="G14">
         <v>1344.8</v>
@@ -2429,28 +2429,28 @@
         <v>304.6</v>
       </c>
       <c r="M14">
-        <v>27.9850536</v>
+        <v>30.3171414</v>
       </c>
       <c r="N14">
-        <v>276.6149464</v>
+        <v>274.2828586</v>
       </c>
       <c r="O14">
-        <v>69.1537366</v>
+        <v>68.57071465</v>
       </c>
       <c r="P14">
-        <v>207.4612098</v>
+        <v>205.71214395</v>
       </c>
       <c r="Q14">
-        <v>326.6612098</v>
+        <v>324.91214395</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09002687427679257</v>
+        <v>0.09041993217118283</v>
       </c>
       <c r="T14">
-        <v>0.8864684298598431</v>
+        <v>0.8943467486463685</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.88438151142222</v>
+        <v>10.04712139515898</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08371584098892906</v>
+        <v>0.08372453261428066</v>
       </c>
       <c r="C15">
-        <v>3955.651807568338</v>
+        <v>3909.898312861367</v>
       </c>
       <c r="D15">
-        <v>3196.124807568338</v>
+        <v>3195.392312861367</v>
       </c>
       <c r="E15">
-        <v>-3.52699999999993</v>
+        <v>41.49400000000014</v>
       </c>
       <c r="F15">
-        <v>585.273</v>
+        <v>630.2940000000001</v>
       </c>
       <c r="G15">
         <v>1344.8</v>
@@ -2511,45 +2511,45 @@
         <v>304.6</v>
       </c>
       <c r="M15">
-        <v>30.3171414</v>
+        <v>33.72072900000001</v>
       </c>
       <c r="N15">
-        <v>274.2828586</v>
+        <v>270.879271</v>
       </c>
       <c r="O15">
-        <v>68.57071465</v>
+        <v>67.71981775</v>
       </c>
       <c r="P15">
-        <v>205.71214395</v>
+        <v>203.15945325</v>
       </c>
       <c r="Q15">
-        <v>324.91214395</v>
+        <v>322.35945325</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09041993217118283</v>
+        <v>0.09082213094683798</v>
       </c>
       <c r="T15">
-        <v>0.8943467486463685</v>
+        <v>0.9024082841488597</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.04712139515898</v>
+        <v>9.033019422563491</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08372453261428066</v>
+        <v>0.08356747423963228</v>
       </c>
       <c r="C16">
-        <v>3909.898312861367</v>
+        <v>3878.165549184444</v>
       </c>
       <c r="D16">
-        <v>3195.392312861367</v>
+        <v>3208.680549184444</v>
       </c>
       <c r="E16">
-        <v>41.49400000000014</v>
+        <v>86.51500000000021</v>
       </c>
       <c r="F16">
-        <v>630.2940000000001</v>
+        <v>675.3150000000002</v>
       </c>
       <c r="G16">
         <v>1344.8</v>
@@ -2593,28 +2593,28 @@
         <v>304.6</v>
       </c>
       <c r="M16">
-        <v>33.72072900000001</v>
+        <v>36.12935250000001</v>
       </c>
       <c r="N16">
-        <v>270.879271</v>
+        <v>268.4706475</v>
       </c>
       <c r="O16">
-        <v>67.71981775</v>
+        <v>67.11766187500001</v>
       </c>
       <c r="P16">
-        <v>203.15945325</v>
+        <v>201.352985625</v>
       </c>
       <c r="Q16">
-        <v>322.35945325</v>
+        <v>320.552985625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09082213094683798</v>
+        <v>0.0912337932230968</v>
       </c>
       <c r="T16">
-        <v>0.9024082841488597</v>
+        <v>0.9106595028396448</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.033019422563491</v>
+        <v>8.430818127725924</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08356747423963228</v>
+        <v>0.08341041586498386</v>
       </c>
       <c r="C17">
-        <v>3878.165549184444</v>
+        <v>3846.543766933857</v>
       </c>
       <c r="D17">
-        <v>3208.680549184444</v>
+        <v>3222.079766933857</v>
       </c>
       <c r="E17">
-        <v>86.5150000000001</v>
+        <v>131.5360000000002</v>
       </c>
       <c r="F17">
-        <v>675.3150000000001</v>
+        <v>720.3360000000001</v>
       </c>
       <c r="G17">
         <v>1344.8</v>
@@ -2675,28 +2675,28 @@
         <v>304.6</v>
       </c>
       <c r="M17">
-        <v>36.1293525</v>
+        <v>38.53797600000001</v>
       </c>
       <c r="N17">
-        <v>268.4706475</v>
+        <v>266.062024</v>
       </c>
       <c r="O17">
-        <v>67.11766187500001</v>
+        <v>66.515506</v>
       </c>
       <c r="P17">
-        <v>201.352985625</v>
+        <v>199.546518</v>
       </c>
       <c r="Q17">
-        <v>320.552985625</v>
+        <v>318.746518</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0912337932230968</v>
+        <v>0.09165525698212366</v>
       </c>
       <c r="T17">
-        <v>0.9106595028396448</v>
+        <v>0.9191071791183056</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.430818127725926</v>
+        <v>7.903891994743055</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08341041586498386</v>
+        <v>0.08335535749033549</v>
       </c>
       <c r="C18">
-        <v>3846.543766933857</v>
+        <v>3806.246526386831</v>
       </c>
       <c r="D18">
-        <v>3222.079766933857</v>
+        <v>3226.803526386831</v>
       </c>
       <c r="E18">
-        <v>131.5360000000002</v>
+        <v>176.5570000000001</v>
       </c>
       <c r="F18">
-        <v>720.3360000000001</v>
+        <v>765.3570000000001</v>
       </c>
       <c r="G18">
         <v>1344.8</v>
@@ -2757,45 +2757,45 @@
         <v>304.6</v>
       </c>
       <c r="M18">
-        <v>38.53797600000001</v>
+        <v>41.5588851</v>
       </c>
       <c r="N18">
-        <v>266.062024</v>
+        <v>263.0411149</v>
       </c>
       <c r="O18">
-        <v>66.515506</v>
+        <v>65.76027872500001</v>
       </c>
       <c r="P18">
-        <v>199.546518</v>
+        <v>197.280836175</v>
       </c>
       <c r="Q18">
-        <v>318.746518</v>
+        <v>316.480836175</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09165525698212366</v>
+        <v>0.0920868764943801</v>
       </c>
       <c r="T18">
-        <v>0.9191071791183056</v>
+        <v>0.9277584138615127</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.903891994743055</v>
+        <v>7.329359275809831</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08335535749033549</v>
+        <v>0.08320429911568708</v>
       </c>
       <c r="C19">
-        <v>3806.246526386831</v>
+        <v>3774.257068416215</v>
       </c>
       <c r="D19">
-        <v>3226.803526386831</v>
+        <v>3239.835068416216</v>
       </c>
       <c r="E19">
-        <v>176.5570000000001</v>
+        <v>221.5780000000002</v>
       </c>
       <c r="F19">
-        <v>765.3570000000001</v>
+        <v>810.3780000000002</v>
       </c>
       <c r="G19">
         <v>1344.8</v>
@@ -2839,28 +2839,28 @@
         <v>304.6</v>
       </c>
       <c r="M19">
-        <v>41.5588851</v>
+        <v>44.00352540000001</v>
       </c>
       <c r="N19">
-        <v>263.0411149</v>
+        <v>260.5964746</v>
       </c>
       <c r="O19">
-        <v>65.76027872500001</v>
+        <v>65.14911865000001</v>
       </c>
       <c r="P19">
-        <v>197.280836175</v>
+        <v>195.44735595</v>
       </c>
       <c r="Q19">
-        <v>316.480836175</v>
+        <v>314.64735595</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0920868764943801</v>
+        <v>0.09252902331181352</v>
       </c>
       <c r="T19">
-        <v>0.9277584138615127</v>
+        <v>0.9366206543301636</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.329359275809831</v>
+        <v>6.922172649375952</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08320429911568709</v>
+        <v>0.0830532407410387</v>
       </c>
       <c r="C20">
-        <v>3774.257068416214</v>
+        <v>3742.373293791205</v>
       </c>
       <c r="D20">
-        <v>3239.835068416214</v>
+        <v>3252.972293791205</v>
       </c>
       <c r="E20">
-        <v>221.5780000000001</v>
+        <v>266.5990000000002</v>
       </c>
       <c r="F20">
-        <v>810.378</v>
+        <v>855.3990000000001</v>
       </c>
       <c r="G20">
         <v>1344.8</v>
@@ -2921,28 +2921,28 @@
         <v>304.6</v>
       </c>
       <c r="M20">
-        <v>44.0035254</v>
+        <v>46.4481657</v>
       </c>
       <c r="N20">
-        <v>260.5964746</v>
+        <v>258.1518343</v>
       </c>
       <c r="O20">
-        <v>65.14911865000001</v>
+        <v>64.537958575</v>
       </c>
       <c r="P20">
-        <v>195.44735595</v>
+        <v>193.613875725</v>
       </c>
       <c r="Q20">
-        <v>314.64735595</v>
+        <v>312.813875725</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09252902331181352</v>
+        <v>0.09298208733461567</v>
       </c>
       <c r="T20">
-        <v>0.9366206543301636</v>
+        <v>0.9457017155511271</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.922172649375953</v>
+        <v>6.557847773093007</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0830532407410387</v>
+        <v>0.0829021823663903</v>
       </c>
       <c r="C21">
-        <v>3742.373293791205</v>
+        <v>3710.596493354019</v>
       </c>
       <c r="D21">
-        <v>3252.972293791205</v>
+        <v>3266.216493354019</v>
       </c>
       <c r="E21">
-        <v>266.5990000000002</v>
+        <v>311.6200000000001</v>
       </c>
       <c r="F21">
-        <v>855.3990000000001</v>
+        <v>900.4200000000001</v>
       </c>
       <c r="G21">
         <v>1344.8</v>
@@ -3003,28 +3003,28 @@
         <v>304.6</v>
       </c>
       <c r="M21">
-        <v>46.4481657</v>
+        <v>48.89280600000001</v>
       </c>
       <c r="N21">
-        <v>258.1518343</v>
+        <v>255.707194</v>
       </c>
       <c r="O21">
-        <v>64.537958575</v>
+        <v>63.9267985</v>
       </c>
       <c r="P21">
-        <v>193.613875725</v>
+        <v>191.7803955</v>
       </c>
       <c r="Q21">
-        <v>312.813875725</v>
+        <v>310.9803955</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09298208733461567</v>
+        <v>0.09344647795798787</v>
       </c>
       <c r="T21">
-        <v>0.9457017155511271</v>
+        <v>0.9550098033026145</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.557847773093007</v>
+        <v>6.229955384438356</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0829021823663903</v>
+        <v>0.0829086239917419</v>
       </c>
       <c r="C22">
-        <v>3710.596493354019</v>
+        <v>3665.00851617448</v>
       </c>
       <c r="D22">
-        <v>3266.216493354019</v>
+        <v>3265.64951617448</v>
       </c>
       <c r="E22">
-        <v>311.6200000000001</v>
+        <v>356.6410000000002</v>
       </c>
       <c r="F22">
-        <v>900.4200000000001</v>
+        <v>945.4410000000001</v>
       </c>
       <c r="G22">
         <v>1344.8</v>
@@ -3085,45 +3085,45 @@
         <v>304.6</v>
       </c>
       <c r="M22">
-        <v>48.89280600000001</v>
+        <v>52.28288730000001</v>
       </c>
       <c r="N22">
-        <v>255.707194</v>
+        <v>252.3171127</v>
       </c>
       <c r="O22">
-        <v>63.9267985</v>
+        <v>63.079278175</v>
       </c>
       <c r="P22">
-        <v>191.7803955</v>
+        <v>189.237834525</v>
       </c>
       <c r="Q22">
-        <v>310.9803955</v>
+        <v>308.437834525</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09344647795798787</v>
+        <v>0.0939226253060024</v>
       </c>
       <c r="T22">
-        <v>0.9550098033026145</v>
+        <v>0.9645535388452788</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.229955384438356</v>
+        <v>5.825998060363433</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0829086239917419</v>
+        <v>0.0827650656170935</v>
       </c>
       <c r="C23">
-        <v>3665.00851617448</v>
+        <v>3632.670067358605</v>
       </c>
       <c r="D23">
-        <v>3265.64951617448</v>
+        <v>3278.332067358605</v>
       </c>
       <c r="E23">
-        <v>356.6410000000001</v>
+        <v>401.6620000000001</v>
       </c>
       <c r="F23">
-        <v>945.441</v>
+        <v>990.4620000000001</v>
       </c>
       <c r="G23">
         <v>1344.8</v>
@@ -3167,28 +3167,28 @@
         <v>304.6</v>
       </c>
       <c r="M23">
-        <v>52.28288730000001</v>
+        <v>54.77254860000001</v>
       </c>
       <c r="N23">
-        <v>252.3171127</v>
+        <v>249.8274514</v>
       </c>
       <c r="O23">
-        <v>63.07927817500001</v>
+        <v>62.45686285000001</v>
       </c>
       <c r="P23">
-        <v>189.237834525</v>
+        <v>187.37058855</v>
       </c>
       <c r="Q23">
-        <v>308.437834525</v>
+        <v>306.57058855</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0939226253060024</v>
+        <v>0.09441098156037628</v>
       </c>
       <c r="T23">
-        <v>0.9645535388452788</v>
+        <v>0.9743419855557037</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.825998060363434</v>
+        <v>5.56117996671055</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0827650656170935</v>
+        <v>0.0826215072424451</v>
       </c>
       <c r="C24">
-        <v>3632.670067358605</v>
+        <v>3600.430511096063</v>
       </c>
       <c r="D24">
-        <v>3278.332067358605</v>
+        <v>3291.113511096064</v>
       </c>
       <c r="E24">
-        <v>401.6620000000001</v>
+        <v>446.6830000000002</v>
       </c>
       <c r="F24">
-        <v>990.4620000000001</v>
+        <v>1035.483</v>
       </c>
       <c r="G24">
         <v>1344.8</v>
@@ -3249,28 +3249,28 @@
         <v>304.6</v>
       </c>
       <c r="M24">
-        <v>54.77254860000001</v>
+        <v>57.26220990000001</v>
       </c>
       <c r="N24">
-        <v>249.8274514</v>
+        <v>247.3377901</v>
       </c>
       <c r="O24">
-        <v>62.45686285000001</v>
+        <v>61.834447525</v>
       </c>
       <c r="P24">
-        <v>187.37058855</v>
+        <v>185.503342575</v>
       </c>
       <c r="Q24">
-        <v>306.57058855</v>
+        <v>304.703342575</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09441098156037628</v>
+        <v>0.09491202239278584</v>
       </c>
       <c r="T24">
-        <v>0.9743419855557037</v>
+        <v>0.9843846776352307</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.56117996671055</v>
+        <v>5.319389533375309</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0826215072424451</v>
+        <v>0.08247794886779672</v>
       </c>
       <c r="C25">
-        <v>3600.430511096063</v>
+        <v>3568.291008590356</v>
       </c>
       <c r="D25">
-        <v>3291.113511096064</v>
+        <v>3303.995008590356</v>
       </c>
       <c r="E25">
-        <v>446.6830000000002</v>
+        <v>491.7040000000002</v>
       </c>
       <c r="F25">
-        <v>1035.483</v>
+        <v>1080.504</v>
       </c>
       <c r="G25">
         <v>1344.8</v>
@@ -3331,28 +3331,28 @@
         <v>304.6</v>
       </c>
       <c r="M25">
-        <v>57.26220990000001</v>
+        <v>59.75187120000001</v>
       </c>
       <c r="N25">
-        <v>247.3377901</v>
+        <v>244.8481288</v>
       </c>
       <c r="O25">
-        <v>61.834447525</v>
+        <v>61.2120322</v>
       </c>
       <c r="P25">
-        <v>185.503342575</v>
+        <v>183.6360966</v>
       </c>
       <c r="Q25">
-        <v>304.703342575</v>
+        <v>302.8360966</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09491202239278584</v>
+        <v>0.09542624851025884</v>
       </c>
       <c r="T25">
-        <v>0.9843846776352307</v>
+        <v>0.9946916510852717</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.319389533375309</v>
+        <v>5.097748302818004</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08247794886779672</v>
+        <v>0.08233439049314831</v>
       </c>
       <c r="C26">
-        <v>3568.291008590356</v>
+        <v>3536.252739296336</v>
       </c>
       <c r="D26">
-        <v>3303.995008590356</v>
+        <v>3316.977739296336</v>
       </c>
       <c r="E26">
-        <v>491.7040000000002</v>
+        <v>536.7250000000001</v>
       </c>
       <c r="F26">
-        <v>1080.504</v>
+        <v>1125.525</v>
       </c>
       <c r="G26">
         <v>1344.8</v>
@@ -3413,28 +3413,28 @@
         <v>304.6</v>
       </c>
       <c r="M26">
-        <v>59.75187120000001</v>
+        <v>62.24153250000001</v>
       </c>
       <c r="N26">
-        <v>244.8481288</v>
+        <v>242.3584675</v>
       </c>
       <c r="O26">
-        <v>61.2120322</v>
+        <v>60.589616875</v>
       </c>
       <c r="P26">
-        <v>183.6360966</v>
+        <v>181.768850625</v>
       </c>
       <c r="Q26">
-        <v>302.8360966</v>
+        <v>300.968850625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09542624851025884</v>
+        <v>0.09595418732419775</v>
       </c>
       <c r="T26">
-        <v>0.9946916510852717</v>
+        <v>1.005273477160647</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.097748302818004</v>
+        <v>4.893838370705284</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08233439049314831</v>
+        <v>0.08219083211849992</v>
       </c>
       <c r="C27">
-        <v>3536.252739296336</v>
+        <v>3504.316901280203</v>
       </c>
       <c r="D27">
-        <v>3316.977739296336</v>
+        <v>3330.062901280203</v>
       </c>
       <c r="E27">
-        <v>536.7250000000001</v>
+        <v>581.7460000000001</v>
       </c>
       <c r="F27">
-        <v>1125.525</v>
+        <v>1170.546</v>
       </c>
       <c r="G27">
         <v>1344.8</v>
@@ -3495,28 +3495,28 @@
         <v>304.6</v>
       </c>
       <c r="M27">
-        <v>62.24153250000001</v>
+        <v>64.7311938</v>
       </c>
       <c r="N27">
-        <v>242.3584675</v>
+        <v>239.8688062</v>
       </c>
       <c r="O27">
-        <v>60.589616875</v>
+        <v>59.96720155000001</v>
       </c>
       <c r="P27">
-        <v>181.768850625</v>
+        <v>179.90160465</v>
       </c>
       <c r="Q27">
-        <v>300.968850625</v>
+        <v>299.10160465</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09595418732419775</v>
+        <v>0.09649639475472963</v>
       </c>
       <c r="T27">
-        <v>1.005273477160647</v>
+        <v>1.016141298535357</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.893838370705284</v>
+        <v>4.705613817985851</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08219083211849992</v>
+        <v>0.08204727374385154</v>
       </c>
       <c r="C28">
-        <v>3504.316901280203</v>
+        <v>3472.484711588061</v>
       </c>
       <c r="D28">
-        <v>3330.062901280203</v>
+        <v>3343.251711588061</v>
       </c>
       <c r="E28">
-        <v>581.7460000000001</v>
+        <v>626.7670000000003</v>
       </c>
       <c r="F28">
-        <v>1170.546</v>
+        <v>1215.567</v>
       </c>
       <c r="G28">
         <v>1344.8</v>
@@ -3577,28 +3577,28 @@
         <v>304.6</v>
       </c>
       <c r="M28">
-        <v>64.7311938</v>
+        <v>67.22085510000001</v>
       </c>
       <c r="N28">
-        <v>239.8688062</v>
+        <v>237.3791449</v>
       </c>
       <c r="O28">
-        <v>59.96720155000001</v>
+        <v>59.34478622500001</v>
       </c>
       <c r="P28">
-        <v>179.90160465</v>
+        <v>178.034358675</v>
       </c>
       <c r="Q28">
-        <v>299.10160465</v>
+        <v>297.234358675</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09649639475472963</v>
+        <v>0.09705345718335827</v>
       </c>
       <c r="T28">
-        <v>1.016141298535357</v>
+        <v>1.02730686844088</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.705613817985851</v>
+        <v>4.531331824727115</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08204727374385154</v>
+        <v>0.08242871536920313</v>
       </c>
       <c r="C29">
-        <v>3472.484711588061</v>
+        <v>3392.647984255732</v>
       </c>
       <c r="D29">
-        <v>3343.251711588061</v>
+        <v>3308.435984255733</v>
       </c>
       <c r="E29">
-        <v>626.7670000000003</v>
+        <v>671.7880000000002</v>
       </c>
       <c r="F29">
-        <v>1215.567</v>
+        <v>1260.588</v>
       </c>
       <c r="G29">
         <v>1344.8</v>
@@ -3659,45 +3659,45 @@
         <v>304.6</v>
       </c>
       <c r="M29">
-        <v>67.22085510000001</v>
+        <v>72.86198640000002</v>
       </c>
       <c r="N29">
-        <v>237.3791449</v>
+        <v>231.7380136</v>
       </c>
       <c r="O29">
-        <v>59.34478622500001</v>
+        <v>57.9345034</v>
       </c>
       <c r="P29">
-        <v>178.034358675</v>
+        <v>173.8035102</v>
       </c>
       <c r="Q29">
-        <v>297.234358675</v>
+        <v>293.0035102</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09705345718335827</v>
+        <v>0.09762599356833768</v>
       </c>
       <c r="T29">
-        <v>1.02730686844088</v>
+        <v>1.038782593066002</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.531331824727115</v>
+        <v>4.180506393660439</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08242871536920313</v>
+        <v>0.08230390699455474</v>
       </c>
       <c r="C30">
-        <v>3392.647984255732</v>
+        <v>3358.938664342053</v>
       </c>
       <c r="D30">
-        <v>3308.435984255733</v>
+        <v>3319.747664342053</v>
       </c>
       <c r="E30">
-        <v>671.7880000000002</v>
+        <v>716.8090000000004</v>
       </c>
       <c r="F30">
-        <v>1260.588</v>
+        <v>1305.609</v>
       </c>
       <c r="G30">
         <v>1344.8</v>
@@ -3741,28 +3741,28 @@
         <v>304.6</v>
       </c>
       <c r="M30">
-        <v>72.86198640000002</v>
+        <v>75.46420020000002</v>
       </c>
       <c r="N30">
-        <v>231.7380136</v>
+        <v>229.1357998</v>
       </c>
       <c r="O30">
-        <v>57.9345034</v>
+        <v>57.28394995</v>
       </c>
       <c r="P30">
-        <v>173.8035102</v>
+        <v>171.85184985</v>
       </c>
       <c r="Q30">
-        <v>293.0035102</v>
+        <v>291.05184985</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09762599356833768</v>
+        <v>0.0982146577388095</v>
       </c>
       <c r="T30">
-        <v>1.038782593066002</v>
+        <v>1.050581577539718</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.180506393660439</v>
+        <v>4.036351000775596</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08230390699455474</v>
+        <v>0.08296659861990634</v>
       </c>
       <c r="C31">
-        <v>3358.938664342053</v>
+        <v>3254.725565599348</v>
       </c>
       <c r="D31">
-        <v>3319.747664342053</v>
+        <v>3260.555565599348</v>
       </c>
       <c r="E31">
-        <v>716.809</v>
+        <v>761.8300000000002</v>
       </c>
       <c r="F31">
-        <v>1305.609</v>
+        <v>1350.63</v>
       </c>
       <c r="G31">
         <v>1344.8</v>
@@ -3823,45 +3823,45 @@
         <v>304.6</v>
       </c>
       <c r="M31">
-        <v>75.46420020000001</v>
+        <v>82.79361900000001</v>
       </c>
       <c r="N31">
-        <v>229.1357998</v>
+        <v>221.806381</v>
       </c>
       <c r="O31">
-        <v>57.28394995000001</v>
+        <v>55.45159525</v>
       </c>
       <c r="P31">
-        <v>171.85184985</v>
+        <v>166.35478575</v>
       </c>
       <c r="Q31">
-        <v>291.05184985</v>
+        <v>285.55478575</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0982146577388095</v>
+        <v>0.0988201408855805</v>
       </c>
       <c r="T31">
-        <v>1.050581577539718</v>
+        <v>1.062717675855541</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.036351000775597</v>
+        <v>3.679027486405686</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08296659861990634</v>
+        <v>0.08286804024525796</v>
       </c>
       <c r="C32">
-        <v>3254.725565599348</v>
+        <v>3218.37389515845</v>
       </c>
       <c r="D32">
-        <v>3260.555565599348</v>
+        <v>3269.22489515845</v>
       </c>
       <c r="E32">
-        <v>761.8300000000002</v>
+        <v>806.8510000000001</v>
       </c>
       <c r="F32">
-        <v>1350.63</v>
+        <v>1395.651</v>
       </c>
       <c r="G32">
         <v>1344.8</v>
@@ -3905,28 +3905,28 @@
         <v>304.6</v>
       </c>
       <c r="M32">
-        <v>82.79361900000001</v>
+        <v>85.55340630000001</v>
       </c>
       <c r="N32">
-        <v>221.806381</v>
+        <v>219.0465937</v>
       </c>
       <c r="O32">
-        <v>55.45159525</v>
+        <v>54.761648425</v>
       </c>
       <c r="P32">
-        <v>166.35478575</v>
+        <v>164.284945275</v>
       </c>
       <c r="Q32">
-        <v>285.55478575</v>
+        <v>283.484945275</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0988201408855805</v>
+        <v>0.09944317426848978</v>
       </c>
       <c r="T32">
-        <v>1.062717675855541</v>
+        <v>1.07520554513704</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.679027486405686</v>
+        <v>3.560349180392599</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08286804024525796</v>
+        <v>0.08344148187060954</v>
       </c>
       <c r="C33">
-        <v>3218.37389515845</v>
+        <v>3123.54854250401</v>
       </c>
       <c r="D33">
-        <v>3269.22489515845</v>
+        <v>3219.42054250401</v>
       </c>
       <c r="E33">
-        <v>806.8510000000001</v>
+        <v>851.8720000000003</v>
       </c>
       <c r="F33">
-        <v>1395.651</v>
+        <v>1440.672</v>
       </c>
       <c r="G33">
         <v>1344.8</v>
@@ -3987,45 +3987,45 @@
         <v>304.6</v>
       </c>
       <c r="M33">
-        <v>85.55340630000001</v>
+        <v>92.34707520000002</v>
       </c>
       <c r="N33">
-        <v>219.0465937</v>
+        <v>212.2529248</v>
       </c>
       <c r="O33">
-        <v>54.761648425</v>
+        <v>53.0632312</v>
       </c>
       <c r="P33">
-        <v>164.284945275</v>
+        <v>159.1896936</v>
       </c>
       <c r="Q33">
-        <v>283.484945275</v>
+        <v>278.3896936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09944317426848978</v>
+        <v>0.1000845321626611</v>
       </c>
       <c r="T33">
-        <v>1.07520554513704</v>
+        <v>1.088060704691524</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.560349180392599</v>
+        <v>3.298426066448935</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08344148187060954</v>
+        <v>0.08336392349596114</v>
       </c>
       <c r="C34">
-        <v>3123.54854250401</v>
+        <v>3085.174692251643</v>
       </c>
       <c r="D34">
-        <v>3219.42054250401</v>
+        <v>3226.067692251643</v>
       </c>
       <c r="E34">
-        <v>851.8720000000003</v>
+        <v>896.8930000000003</v>
       </c>
       <c r="F34">
-        <v>1440.672</v>
+        <v>1485.693</v>
       </c>
       <c r="G34">
         <v>1344.8</v>
@@ -4069,28 +4069,28 @@
         <v>304.6</v>
       </c>
       <c r="M34">
-        <v>92.34707520000002</v>
+        <v>95.23292130000002</v>
       </c>
       <c r="N34">
-        <v>212.2529248</v>
+        <v>209.3670787</v>
       </c>
       <c r="O34">
-        <v>53.0632312</v>
+        <v>52.341769675</v>
       </c>
       <c r="P34">
-        <v>159.1896936</v>
+        <v>157.025309025</v>
       </c>
       <c r="Q34">
-        <v>278.3896936</v>
+        <v>276.225309025</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1000845321626611</v>
+        <v>0.1007450350685987</v>
       </c>
       <c r="T34">
-        <v>1.088060704691524</v>
+        <v>1.101299600352112</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.298426066448935</v>
+        <v>3.198473761405028</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08336392349596114</v>
+        <v>0.08328636512131275</v>
       </c>
       <c r="C35">
-        <v>3085.174692251643</v>
+        <v>3046.828347580507</v>
       </c>
       <c r="D35">
-        <v>3226.067692251643</v>
+        <v>3232.742347580507</v>
       </c>
       <c r="E35">
-        <v>896.8930000000003</v>
+        <v>941.9140000000002</v>
       </c>
       <c r="F35">
-        <v>1485.693</v>
+        <v>1530.714</v>
       </c>
       <c r="G35">
         <v>1344.8</v>
@@ -4151,28 +4151,28 @@
         <v>304.6</v>
       </c>
       <c r="M35">
-        <v>95.23292130000002</v>
+        <v>98.11876740000002</v>
       </c>
       <c r="N35">
-        <v>209.3670787</v>
+        <v>206.4812326</v>
       </c>
       <c r="O35">
-        <v>52.341769675</v>
+        <v>51.62030815</v>
       </c>
       <c r="P35">
-        <v>157.025309025</v>
+        <v>154.86092445</v>
       </c>
       <c r="Q35">
-        <v>276.225309025</v>
+        <v>274.06092445</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1007450350685987</v>
+        <v>0.1014255532141102</v>
       </c>
       <c r="T35">
-        <v>1.101299600352112</v>
+        <v>1.114939674669081</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.198473761405028</v>
+        <v>3.104401003716644</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08328636512131275</v>
+        <v>0.08320880674666437</v>
       </c>
       <c r="C36">
-        <v>3046.828347580507</v>
+        <v>3008.50967956969</v>
       </c>
       <c r="D36">
-        <v>3232.742347580507</v>
+        <v>3239.444679569691</v>
       </c>
       <c r="E36">
-        <v>941.9140000000002</v>
+        <v>986.9350000000004</v>
       </c>
       <c r="F36">
-        <v>1530.714</v>
+        <v>1575.735</v>
       </c>
       <c r="G36">
         <v>1344.8</v>
@@ -4233,28 +4233,28 @@
         <v>304.6</v>
       </c>
       <c r="M36">
-        <v>98.11876740000002</v>
+        <v>101.0046135</v>
       </c>
       <c r="N36">
-        <v>206.4812326</v>
+        <v>203.5953865</v>
       </c>
       <c r="O36">
-        <v>51.62030815</v>
+        <v>50.898846625</v>
       </c>
       <c r="P36">
-        <v>154.86092445</v>
+        <v>152.696539875</v>
       </c>
       <c r="Q36">
-        <v>274.06092445</v>
+        <v>271.896539875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1014255532141102</v>
+        <v>0.1021270103794836</v>
       </c>
       <c r="T36">
-        <v>1.114939674669081</v>
+        <v>1.128999443580419</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.104401003716644</v>
+        <v>3.015703832181883</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08320880674666437</v>
+        <v>0.08523724837201596</v>
       </c>
       <c r="C37">
-        <v>3008.50967956969</v>
+        <v>2796.868930415852</v>
       </c>
       <c r="D37">
-        <v>3239.444679569691</v>
+        <v>3072.824930415853</v>
       </c>
       <c r="E37">
-        <v>986.9350000000004</v>
+        <v>1031.956</v>
       </c>
       <c r="F37">
-        <v>1575.735</v>
+        <v>1620.756</v>
       </c>
       <c r="G37">
         <v>1344.8</v>
@@ -4315,45 +4315,45 @@
         <v>304.6</v>
       </c>
       <c r="M37">
-        <v>101.0046135</v>
+        <v>116.5323564</v>
       </c>
       <c r="N37">
-        <v>203.5953865</v>
+        <v>188.0676436</v>
       </c>
       <c r="O37">
-        <v>50.898846625</v>
+        <v>47.0169109</v>
       </c>
       <c r="P37">
-        <v>152.696539875</v>
+        <v>141.0507327</v>
       </c>
       <c r="Q37">
-        <v>271.896539875</v>
+        <v>260.2507327</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1021270103794836</v>
+        <v>0.1028503880812749</v>
       </c>
       <c r="T37">
-        <v>1.128999443580419</v>
+        <v>1.143498580270236</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.015703832181883</v>
+        <v>2.613866306405523</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08523724837201596</v>
+        <v>0.08521818999736758</v>
       </c>
       <c r="C38">
-        <v>2796.868930415852</v>
+        <v>2753.333616307485</v>
       </c>
       <c r="D38">
-        <v>3072.824930415853</v>
+        <v>3074.310616307484</v>
       </c>
       <c r="E38">
-        <v>1031.956</v>
+        <v>1076.977</v>
       </c>
       <c r="F38">
-        <v>1620.756</v>
+        <v>1665.777</v>
       </c>
       <c r="G38">
         <v>1344.8</v>
@@ -4397,28 +4397,28 @@
         <v>304.6</v>
       </c>
       <c r="M38">
-        <v>116.5323564</v>
+        <v>119.7693663</v>
       </c>
       <c r="N38">
-        <v>188.0676436</v>
+        <v>184.8306337</v>
       </c>
       <c r="O38">
-        <v>47.0169109</v>
+        <v>46.20765842500001</v>
       </c>
       <c r="P38">
-        <v>141.0507327</v>
+        <v>138.622975275</v>
       </c>
       <c r="Q38">
-        <v>260.2507327</v>
+        <v>257.822975275</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1028503880812749</v>
+        <v>0.1035967301545517</v>
       </c>
       <c r="T38">
-        <v>1.143498580270236</v>
+        <v>1.158458007013698</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.613866306405523</v>
+        <v>2.543221271097265</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08521818999736758</v>
+        <v>0.08631063162271918</v>
       </c>
       <c r="C39">
-        <v>2753.333616307485</v>
+        <v>2625.408332864243</v>
       </c>
       <c r="D39">
-        <v>3074.310616307484</v>
+        <v>2991.406332864244</v>
       </c>
       <c r="E39">
-        <v>1076.977</v>
+        <v>1121.998</v>
       </c>
       <c r="F39">
-        <v>1665.777</v>
+        <v>1710.798</v>
       </c>
       <c r="G39">
         <v>1344.8</v>
@@ -4479,45 +4479,45 @@
         <v>304.6</v>
       </c>
       <c r="M39">
-        <v>119.7693663</v>
+        <v>129.6784884</v>
       </c>
       <c r="N39">
-        <v>184.8306337</v>
+        <v>174.9215116</v>
       </c>
       <c r="O39">
-        <v>46.20765842500001</v>
+        <v>43.7303779</v>
       </c>
       <c r="P39">
-        <v>138.622975275</v>
+        <v>131.1911337</v>
       </c>
       <c r="Q39">
-        <v>257.822975275</v>
+        <v>250.3911337</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1035967301545517</v>
+        <v>0.1043671477785793</v>
       </c>
       <c r="T39">
-        <v>1.158458007013698</v>
+        <v>1.173899995910175</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.543221271097265</v>
+        <v>2.348886108700199</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08631063162271918</v>
+        <v>0.08632082324807078</v>
       </c>
       <c r="C40">
-        <v>2625.408332864243</v>
+        <v>2579.634947049367</v>
       </c>
       <c r="D40">
-        <v>2991.406332864244</v>
+        <v>2990.653947049368</v>
       </c>
       <c r="E40">
-        <v>1121.998</v>
+        <v>1167.019</v>
       </c>
       <c r="F40">
-        <v>1710.798</v>
+        <v>1755.819</v>
       </c>
       <c r="G40">
         <v>1344.8</v>
@@ -4561,28 +4561,28 @@
         <v>304.6</v>
       </c>
       <c r="M40">
-        <v>129.6784884</v>
+        <v>133.0910802</v>
       </c>
       <c r="N40">
-        <v>174.9215116</v>
+        <v>171.5089198</v>
       </c>
       <c r="O40">
-        <v>43.7303779</v>
+        <v>42.87722995</v>
       </c>
       <c r="P40">
-        <v>131.1911337</v>
+        <v>128.63168985</v>
       </c>
       <c r="Q40">
-        <v>250.3911337</v>
+        <v>247.83168985</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1043671477785793</v>
+        <v>0.1051628249968374</v>
       </c>
       <c r="T40">
-        <v>1.173899995910175</v>
+        <v>1.189848279524569</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.348886108700199</v>
+        <v>2.288658259759169</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08632082324807078</v>
+        <v>0.08633101487342237</v>
       </c>
       <c r="C41">
-        <v>2579.634947049367</v>
+        <v>2533.861939613092</v>
       </c>
       <c r="D41">
-        <v>2990.653947049368</v>
+        <v>2989.901939613092</v>
       </c>
       <c r="E41">
-        <v>1167.019</v>
+        <v>1212.04</v>
       </c>
       <c r="F41">
-        <v>1755.819</v>
+        <v>1800.84</v>
       </c>
       <c r="G41">
         <v>1344.8</v>
@@ -4643,28 +4643,28 @@
         <v>304.6</v>
       </c>
       <c r="M41">
-        <v>133.0910802</v>
+        <v>136.503672</v>
       </c>
       <c r="N41">
-        <v>171.5089198</v>
+        <v>168.096328</v>
       </c>
       <c r="O41">
-        <v>42.87722995</v>
+        <v>42.024082</v>
       </c>
       <c r="P41">
-        <v>128.63168985</v>
+        <v>126.072246</v>
       </c>
       <c r="Q41">
-        <v>247.83168985</v>
+        <v>245.272246</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1051628249968374</v>
+        <v>0.1059850247890373</v>
       </c>
       <c r="T41">
-        <v>1.189848279524569</v>
+        <v>1.206328172592776</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.288658259759169</v>
+        <v>2.23144180326519</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08633101487342237</v>
+        <v>0.086341206498774</v>
       </c>
       <c r="C42">
-        <v>2533.861939613092</v>
+        <v>2488.089310270054</v>
       </c>
       <c r="D42">
-        <v>2989.901939613092</v>
+        <v>2989.150310270054</v>
       </c>
       <c r="E42">
-        <v>1212.04</v>
+        <v>1257.061</v>
       </c>
       <c r="F42">
-        <v>1800.84</v>
+        <v>1845.861</v>
       </c>
       <c r="G42">
         <v>1344.8</v>
@@ -4725,28 +4725,28 @@
         <v>304.6</v>
       </c>
       <c r="M42">
-        <v>136.503672</v>
+        <v>139.9162638</v>
       </c>
       <c r="N42">
-        <v>168.096328</v>
+        <v>164.6837362</v>
       </c>
       <c r="O42">
-        <v>42.024082</v>
+        <v>41.17093405</v>
       </c>
       <c r="P42">
-        <v>126.072246</v>
+        <v>123.51280215</v>
       </c>
       <c r="Q42">
-        <v>245.272246</v>
+        <v>242.71280215</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1059850247890373</v>
+        <v>0.1068350957606339</v>
       </c>
       <c r="T42">
-        <v>1.206328172592776</v>
+        <v>1.223366706103974</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.23144180326519</v>
+        <v>2.177016393429454</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.086341206498774</v>
+        <v>0.08635139812412559</v>
       </c>
       <c r="C43">
-        <v>2488.089310270054</v>
+        <v>2442.317058735183</v>
       </c>
       <c r="D43">
-        <v>2989.150310270054</v>
+        <v>2988.399058735184</v>
       </c>
       <c r="E43">
-        <v>1257.061</v>
+        <v>1302.082</v>
       </c>
       <c r="F43">
-        <v>1845.861</v>
+        <v>1890.882</v>
       </c>
       <c r="G43">
         <v>1344.8</v>
@@ -4807,28 +4807,28 @@
         <v>304.6</v>
       </c>
       <c r="M43">
-        <v>139.9162638</v>
+        <v>143.3288556</v>
       </c>
       <c r="N43">
-        <v>164.6837362</v>
+        <v>161.2711444</v>
       </c>
       <c r="O43">
-        <v>41.17093405</v>
+        <v>40.3177861</v>
       </c>
       <c r="P43">
-        <v>123.51280215</v>
+        <v>120.9533583</v>
       </c>
       <c r="Q43">
-        <v>242.71280215</v>
+        <v>240.1533583</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1068350957606339</v>
+        <v>0.1077144795243545</v>
       </c>
       <c r="T43">
-        <v>1.223366706103974</v>
+        <v>1.240992775253488</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.177016393429454</v>
+        <v>2.125182669776371</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08635139812412561</v>
+        <v>0.08636158974947721</v>
       </c>
       <c r="C44">
-        <v>2442.317058735183</v>
+        <v>2396.545184723691</v>
       </c>
       <c r="D44">
-        <v>2988.399058735183</v>
+        <v>2987.648184723691</v>
       </c>
       <c r="E44">
-        <v>1302.082</v>
+        <v>1347.103</v>
       </c>
       <c r="F44">
-        <v>1890.882</v>
+        <v>1935.903</v>
       </c>
       <c r="G44">
         <v>1344.8</v>
@@ -4889,28 +4889,28 @@
         <v>304.6</v>
       </c>
       <c r="M44">
-        <v>143.3288556</v>
+        <v>146.7414474</v>
       </c>
       <c r="N44">
-        <v>161.2711444</v>
+        <v>157.8585526</v>
       </c>
       <c r="O44">
-        <v>40.3177861</v>
+        <v>39.46463815</v>
       </c>
       <c r="P44">
-        <v>120.9533583</v>
+        <v>118.39391445</v>
       </c>
       <c r="Q44">
-        <v>240.1533583</v>
+        <v>237.59391445</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1077144795243545</v>
+        <v>0.1086247188587319</v>
       </c>
       <c r="T44">
-        <v>1.240992775253488</v>
+        <v>1.259237302969652</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.125182669776371</v>
+        <v>2.075759816990874</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08636158974947721</v>
+        <v>0.08637178137482882</v>
       </c>
       <c r="C45">
-        <v>2396.545184723691</v>
+        <v>2350.773687951074</v>
       </c>
       <c r="D45">
-        <v>2987.648184723691</v>
+        <v>2986.897687951074</v>
       </c>
       <c r="E45">
-        <v>1347.103</v>
+        <v>1392.124</v>
       </c>
       <c r="F45">
-        <v>1935.903</v>
+        <v>1980.924</v>
       </c>
       <c r="G45">
         <v>1344.8</v>
@@ -4971,28 +4971,28 @@
         <v>304.6</v>
       </c>
       <c r="M45">
-        <v>146.7414474</v>
+        <v>150.1540392</v>
       </c>
       <c r="N45">
-        <v>157.8585526</v>
+        <v>154.4459608</v>
       </c>
       <c r="O45">
-        <v>39.46463815</v>
+        <v>38.6114902</v>
       </c>
       <c r="P45">
-        <v>118.39391445</v>
+        <v>115.8344706</v>
       </c>
       <c r="Q45">
-        <v>237.59391445</v>
+        <v>235.0344706</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1086247188587319</v>
+        <v>0.1095674667407657</v>
       </c>
       <c r="T45">
-        <v>1.259237302969652</v>
+        <v>1.278133420961394</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.075759816990874</v>
+        <v>2.028583457513808</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08637178137482882</v>
+        <v>0.09117447300018042</v>
       </c>
       <c r="C46">
-        <v>2350.773687951074</v>
+        <v>1989.602492407257</v>
       </c>
       <c r="D46">
-        <v>2986.897687951074</v>
+        <v>2670.747492407257</v>
       </c>
       <c r="E46">
-        <v>1392.124</v>
+        <v>1437.145</v>
       </c>
       <c r="F46">
-        <v>1980.924</v>
+        <v>2025.945</v>
       </c>
       <c r="G46">
         <v>1344.8</v>
@@ -5053,45 +5053,45 @@
         <v>304.6</v>
       </c>
       <c r="M46">
-        <v>150.1540392</v>
+        <v>182.33505</v>
       </c>
       <c r="N46">
-        <v>154.4459608</v>
+        <v>122.26495</v>
       </c>
       <c r="O46">
-        <v>38.6114902</v>
+        <v>30.56623750000001</v>
       </c>
       <c r="P46">
-        <v>115.8344706</v>
+        <v>91.69871250000003</v>
       </c>
       <c r="Q46">
-        <v>235.0344706</v>
+        <v>210.8987125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1095674667407657</v>
+        <v>0.1105444963639644</v>
       </c>
       <c r="T46">
-        <v>1.278133420961394</v>
+        <v>1.297716670516471</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.028583457513808</v>
+        <v>1.67055099938273</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09117447300018042</v>
+        <v>0.09129116462553202</v>
       </c>
       <c r="C47">
-        <v>1989.602492407257</v>
+        <v>1937.730626566425</v>
       </c>
       <c r="D47">
-        <v>2670.747492407257</v>
+        <v>2663.896626566425</v>
       </c>
       <c r="E47">
-        <v>1437.145</v>
+        <v>1482.166</v>
       </c>
       <c r="F47">
-        <v>2025.945</v>
+        <v>2070.966</v>
       </c>
       <c r="G47">
         <v>1344.8</v>
@@ -5135,28 +5135,28 @@
         <v>304.6</v>
       </c>
       <c r="M47">
-        <v>182.33505</v>
+        <v>186.38694</v>
       </c>
       <c r="N47">
-        <v>122.26495</v>
+        <v>118.21306</v>
       </c>
       <c r="O47">
-        <v>30.56623750000001</v>
+        <v>29.553265</v>
       </c>
       <c r="P47">
-        <v>91.69871250000003</v>
+        <v>88.65979499999999</v>
       </c>
       <c r="Q47">
-        <v>210.8987125</v>
+        <v>207.859795</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1105444963639644</v>
+        <v>0.1115577122695037</v>
       </c>
       <c r="T47">
-        <v>1.297716670516471</v>
+        <v>1.318025225610626</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.67055099938273</v>
+        <v>1.634234673309192</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09129116462553202</v>
+        <v>0.09140785625088363</v>
       </c>
       <c r="C48">
-        <v>1937.730626566425</v>
+        <v>1885.893817785308</v>
       </c>
       <c r="D48">
-        <v>2663.896626566425</v>
+        <v>2657.080817785308</v>
       </c>
       <c r="E48">
-        <v>1482.166</v>
+        <v>1527.187</v>
       </c>
       <c r="F48">
-        <v>2070.966</v>
+        <v>2115.987</v>
       </c>
       <c r="G48">
         <v>1344.8</v>
@@ -5217,28 +5217,28 @@
         <v>304.6</v>
       </c>
       <c r="M48">
-        <v>186.38694</v>
+        <v>190.43883</v>
       </c>
       <c r="N48">
-        <v>118.21306</v>
+        <v>114.16117</v>
       </c>
       <c r="O48">
-        <v>29.553265</v>
+        <v>28.54029250000001</v>
       </c>
       <c r="P48">
-        <v>88.65979499999999</v>
+        <v>85.62087750000002</v>
       </c>
       <c r="Q48">
-        <v>207.859795</v>
+        <v>204.8208775</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1115577122695037</v>
+        <v>0.1126091627375163</v>
       </c>
       <c r="T48">
-        <v>1.318025225610626</v>
+        <v>1.339100141274371</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.634234673309192</v>
+        <v>1.599463722813252</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09140785625088363</v>
+        <v>0.09152454787623522</v>
       </c>
       <c r="C49">
-        <v>1885.893817785308</v>
+        <v>1834.091797661125</v>
       </c>
       <c r="D49">
-        <v>2657.080817785308</v>
+        <v>2650.299797661125</v>
       </c>
       <c r="E49">
-        <v>1527.187</v>
+        <v>1572.208</v>
       </c>
       <c r="F49">
-        <v>2115.987</v>
+        <v>2161.008</v>
       </c>
       <c r="G49">
         <v>1344.8</v>
@@ -5299,28 +5299,28 @@
         <v>304.6</v>
       </c>
       <c r="M49">
-        <v>190.43883</v>
+        <v>194.49072</v>
       </c>
       <c r="N49">
-        <v>114.16117</v>
+        <v>110.10928</v>
       </c>
       <c r="O49">
-        <v>28.54029250000001</v>
+        <v>27.52732</v>
       </c>
       <c r="P49">
-        <v>85.62087750000002</v>
+        <v>82.58196000000001</v>
       </c>
       <c r="Q49">
-        <v>204.8208775</v>
+        <v>201.78196</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1126091627375163</v>
+        <v>0.1137010536081446</v>
       </c>
       <c r="T49">
-        <v>1.339100141274371</v>
+        <v>1.360985630617491</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.599463722813252</v>
+        <v>1.566141561921309</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09152454787623521</v>
+        <v>0.09164123950158684</v>
       </c>
       <c r="C50">
-        <v>1834.091797661126</v>
+        <v>1782.324300524034</v>
       </c>
       <c r="D50">
-        <v>2650.299797661126</v>
+        <v>2643.553300524035</v>
       </c>
       <c r="E50">
-        <v>1572.208</v>
+        <v>1617.229</v>
       </c>
       <c r="F50">
-        <v>2161.008</v>
+        <v>2206.029</v>
       </c>
       <c r="G50">
         <v>1344.8</v>
@@ -5381,28 +5381,28 @@
         <v>304.6</v>
       </c>
       <c r="M50">
-        <v>194.49072</v>
+        <v>198.54261</v>
       </c>
       <c r="N50">
-        <v>110.10928</v>
+        <v>106.05739</v>
       </c>
       <c r="O50">
-        <v>27.52732</v>
+        <v>26.51434750000001</v>
       </c>
       <c r="P50">
-        <v>82.58196000000001</v>
+        <v>79.54304250000001</v>
       </c>
       <c r="Q50">
-        <v>201.78196</v>
+        <v>198.7430425</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1137010536081446</v>
+        <v>0.1148357637286016</v>
       </c>
       <c r="T50">
-        <v>1.360985630617491</v>
+        <v>1.383729374444655</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.566141561921309</v>
+        <v>1.534179489229038</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09164123950158684</v>
+        <v>0.09175793112693843</v>
       </c>
       <c r="C51">
-        <v>1782.324300524034</v>
+        <v>1730.591063402444</v>
       </c>
       <c r="D51">
-        <v>2643.553300524035</v>
+        <v>2636.841063402444</v>
       </c>
       <c r="E51">
-        <v>1617.229</v>
+        <v>1662.25</v>
       </c>
       <c r="F51">
-        <v>2206.029</v>
+        <v>2251.05</v>
       </c>
       <c r="G51">
         <v>1344.8</v>
@@ -5463,28 +5463,28 @@
         <v>304.6</v>
       </c>
       <c r="M51">
-        <v>198.54261</v>
+        <v>202.5945</v>
       </c>
       <c r="N51">
-        <v>106.05739</v>
+        <v>102.0055</v>
       </c>
       <c r="O51">
-        <v>26.51434750000001</v>
+        <v>25.501375</v>
       </c>
       <c r="P51">
-        <v>79.54304250000001</v>
+        <v>76.50412500000002</v>
       </c>
       <c r="Q51">
-        <v>198.7430425</v>
+        <v>195.704125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1148357637286016</v>
+        <v>0.1160158622538769</v>
       </c>
       <c r="T51">
-        <v>1.383729374444655</v>
+        <v>1.407382868024906</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.534179489229038</v>
+        <v>1.503495899444457</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09175793112693843</v>
+        <v>0.1158959996361319</v>
       </c>
       <c r="C52">
-        <v>1730.591063402444</v>
+        <v>777.5546193448577</v>
       </c>
       <c r="D52">
-        <v>2636.841063402444</v>
+        <v>1728.825619344858</v>
       </c>
       <c r="E52">
-        <v>1662.25</v>
+        <v>1707.271</v>
       </c>
       <c r="F52">
-        <v>2251.05</v>
+        <v>2296.071</v>
       </c>
       <c r="G52">
         <v>1344.8</v>
@@ -5545,45 +5545,45 @@
         <v>304.6</v>
       </c>
       <c r="M52">
-        <v>202.5945</v>
+        <v>337.0632228000001</v>
       </c>
       <c r="N52">
-        <v>102.0055</v>
+        <v>-32.46322280000004</v>
       </c>
       <c r="O52">
-        <v>25.501375</v>
+        <v>-8.11580570000001</v>
       </c>
       <c r="P52">
-        <v>76.50412500000002</v>
+        <v>-24.34741710000003</v>
       </c>
       <c r="Q52">
-        <v>195.704125</v>
+        <v>94.85258289999996</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1160158622538769</v>
+        <v>0.1182496500099633</v>
       </c>
       <c r="T52">
-        <v>1.407382868024906</v>
+        <v>1.452156150269208</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.25</v>
+        <v>0.2259220076501327</v>
       </c>
       <c r="W52">
-        <v>0.0675</v>
+        <v>0.1136346492769605</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.503495899444457</v>
+        <v>0.9036880306005309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1158959996361319</v>
+        <v>0.1169059996361319</v>
       </c>
       <c r="C53">
-        <v>777.5546193448577</v>
+        <v>707.977127846621</v>
       </c>
       <c r="D53">
-        <v>1728.825619344858</v>
+        <v>1704.269127846621</v>
       </c>
       <c r="E53">
-        <v>1707.271</v>
+        <v>1752.292</v>
       </c>
       <c r="F53">
-        <v>2296.071</v>
+        <v>2341.092</v>
       </c>
       <c r="G53">
         <v>1344.8</v>
@@ -5627,37 +5627,37 @@
         <v>304.6</v>
       </c>
       <c r="M53">
-        <v>337.0632228000001</v>
+        <v>343.6723056000001</v>
       </c>
       <c r="N53">
-        <v>-32.46322280000004</v>
+        <v>-39.07230560000005</v>
       </c>
       <c r="O53">
-        <v>-8.11580570000001</v>
+        <v>-9.768076400000012</v>
       </c>
       <c r="P53">
-        <v>-24.34741710000003</v>
+        <v>-29.30422920000004</v>
       </c>
       <c r="Q53">
-        <v>94.85258289999996</v>
+        <v>89.89577079999995</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1182496500099633</v>
+        <v>0.1197590177185042</v>
       </c>
       <c r="T53">
-        <v>1.452156150269208</v>
+        <v>1.482409403399816</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2259220076501327</v>
+        <v>0.2215773536568609</v>
       </c>
       <c r="W53">
-        <v>0.1136346492769605</v>
+        <v>0.1142724444831728</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9036880306005309</v>
+        <v>0.8863094146274437</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1169059996361319</v>
+        <v>0.1179159996361319</v>
       </c>
       <c r="C54">
-        <v>707.977127846621</v>
+        <v>639.0874741801645</v>
       </c>
       <c r="D54">
-        <v>1704.269127846621</v>
+        <v>1680.400474180165</v>
       </c>
       <c r="E54">
-        <v>1752.292</v>
+        <v>1797.313</v>
       </c>
       <c r="F54">
-        <v>2341.092</v>
+        <v>2386.113</v>
       </c>
       <c r="G54">
         <v>1344.8</v>
@@ -5709,37 +5709,37 @@
         <v>304.6</v>
       </c>
       <c r="M54">
-        <v>343.6723056000001</v>
+        <v>350.2813884000001</v>
       </c>
       <c r="N54">
-        <v>-39.07230560000005</v>
+        <v>-45.68138840000006</v>
       </c>
       <c r="O54">
-        <v>-9.768076400000012</v>
+        <v>-11.42034710000001</v>
       </c>
       <c r="P54">
-        <v>-29.30422920000004</v>
+        <v>-34.26104130000004</v>
       </c>
       <c r="Q54">
-        <v>89.89577079999995</v>
+        <v>84.93895869999994</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1197590177185042</v>
+        <v>0.1213326138401745</v>
       </c>
       <c r="T54">
-        <v>1.482409403399816</v>
+        <v>1.513950029004067</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2215773536568609</v>
+        <v>0.2173966488708824</v>
       </c>
       <c r="W54">
-        <v>0.1142724444831728</v>
+        <v>0.1148861719457545</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8863094146274437</v>
+        <v>0.8695865954835297</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1179159996361319</v>
+        <v>0.1189259996361319</v>
       </c>
       <c r="C55">
-        <v>639.0874741801645</v>
+        <v>570.8571575572528</v>
       </c>
       <c r="D55">
-        <v>1680.400474180165</v>
+        <v>1657.191157557253</v>
       </c>
       <c r="E55">
-        <v>1797.313</v>
+        <v>1842.334000000001</v>
       </c>
       <c r="F55">
-        <v>2386.113</v>
+        <v>2431.134</v>
       </c>
       <c r="G55">
         <v>1344.8</v>
@@ -5791,37 +5791,37 @@
         <v>304.6</v>
       </c>
       <c r="M55">
-        <v>350.2813884000001</v>
+        <v>356.8904712000001</v>
       </c>
       <c r="N55">
-        <v>-45.68138840000006</v>
+        <v>-52.29047120000007</v>
       </c>
       <c r="O55">
-        <v>-11.42034710000001</v>
+        <v>-13.07261780000002</v>
       </c>
       <c r="P55">
-        <v>-34.26104130000004</v>
+        <v>-39.21785340000005</v>
       </c>
       <c r="Q55">
-        <v>84.93895869999994</v>
+        <v>79.98214659999994</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1213326138401745</v>
+        <v>0.1229746271845261</v>
       </c>
       <c r="T55">
-        <v>1.513950029004067</v>
+        <v>1.54686198615633</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2173966488708824</v>
+        <v>0.2133707850029031</v>
       </c>
       <c r="W55">
-        <v>0.1148861719457545</v>
+        <v>0.1154771687615738</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8695865954835297</v>
+        <v>0.8534831400116125</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1189259996361319</v>
+        <v>0.1199359996361319</v>
       </c>
       <c r="C56">
-        <v>570.8571575572528</v>
+        <v>503.2592303242232</v>
       </c>
       <c r="D56">
-        <v>1657.191157557253</v>
+        <v>1634.614230324223</v>
       </c>
       <c r="E56">
-        <v>1842.334000000001</v>
+        <v>1887.355</v>
       </c>
       <c r="F56">
-        <v>2431.134</v>
+        <v>2476.155</v>
       </c>
       <c r="G56">
         <v>1344.8</v>
@@ -5873,37 +5873,37 @@
         <v>304.6</v>
       </c>
       <c r="M56">
-        <v>356.8904712000001</v>
+        <v>363.499554</v>
       </c>
       <c r="N56">
-        <v>-52.29047120000007</v>
+        <v>-58.89955400000002</v>
       </c>
       <c r="O56">
-        <v>-13.07261780000002</v>
+        <v>-14.72488850000001</v>
       </c>
       <c r="P56">
-        <v>-39.21785340000005</v>
+        <v>-44.17466550000002</v>
       </c>
       <c r="Q56">
-        <v>79.98214659999994</v>
+        <v>75.02533449999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1229746271845261</v>
+        <v>0.1246896188997378</v>
       </c>
       <c r="T56">
-        <v>1.54686198615633</v>
+        <v>1.581236696959804</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2133707850029031</v>
+        <v>0.2094913161846685</v>
       </c>
       <c r="W56">
-        <v>0.1154771687615738</v>
+        <v>0.1160466747840907</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8534831400116125</v>
+        <v>0.8379652647386742</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1199359996361319</v>
+        <v>0.1209459996361319</v>
       </c>
       <c r="C57">
-        <v>503.2592303242232</v>
+        <v>436.2681935874489</v>
       </c>
       <c r="D57">
-        <v>1634.614230324223</v>
+        <v>1612.644193587449</v>
       </c>
       <c r="E57">
-        <v>1887.355</v>
+        <v>1932.376</v>
       </c>
       <c r="F57">
-        <v>2476.155</v>
+        <v>2521.176</v>
       </c>
       <c r="G57">
         <v>1344.8</v>
@@ -5955,37 +5955,37 @@
         <v>304.6</v>
       </c>
       <c r="M57">
-        <v>363.499554</v>
+        <v>370.1086368000001</v>
       </c>
       <c r="N57">
-        <v>-58.89955400000002</v>
+        <v>-65.50863680000009</v>
       </c>
       <c r="O57">
-        <v>-14.72488850000001</v>
+        <v>-16.37715920000002</v>
       </c>
       <c r="P57">
-        <v>-44.17466550000002</v>
+        <v>-49.13147760000007</v>
       </c>
       <c r="Q57">
-        <v>75.02533449999997</v>
+        <v>70.06852239999992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1246896188997378</v>
+        <v>0.1264825647838228</v>
       </c>
       <c r="T57">
-        <v>1.581236696959804</v>
+        <v>1.617173894617981</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2094913161846685</v>
+        <v>0.205750399824228</v>
       </c>
       <c r="W57">
-        <v>0.1160466747840907</v>
+        <v>0.1165958413058033</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8379652647386742</v>
+        <v>0.823001599296912</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1209459996361319</v>
+        <v>0.1219559996361319</v>
       </c>
       <c r="C58">
-        <v>436.2681935874489</v>
+        <v>369.8599011442325</v>
       </c>
       <c r="D58">
-        <v>1612.644193587449</v>
+        <v>1591.256901144233</v>
       </c>
       <c r="E58">
-        <v>1932.376</v>
+        <v>1977.397000000001</v>
       </c>
       <c r="F58">
-        <v>2521.176</v>
+        <v>2566.197000000001</v>
       </c>
       <c r="G58">
         <v>1344.8</v>
@@ -6037,37 +6037,37 @@
         <v>304.6</v>
       </c>
       <c r="M58">
-        <v>370.1086368000001</v>
+        <v>376.7177196000001</v>
       </c>
       <c r="N58">
-        <v>-65.50863680000009</v>
+        <v>-72.1177196000001</v>
       </c>
       <c r="O58">
-        <v>-16.37715920000002</v>
+        <v>-18.02942990000003</v>
       </c>
       <c r="P58">
-        <v>-49.13147760000007</v>
+        <v>-54.08828970000008</v>
       </c>
       <c r="Q58">
-        <v>70.06852239999992</v>
+        <v>65.11171029999991</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1264825647838228</v>
+        <v>0.1283589034997256</v>
       </c>
       <c r="T58">
-        <v>1.617173894617981</v>
+        <v>1.654782589841655</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.205750399824228</v>
+        <v>0.2021407436869608</v>
       </c>
       <c r="W58">
-        <v>0.1165958413058033</v>
+        <v>0.1171257388267542</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.823001599296912</v>
+        <v>0.8085629747478433</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1219559996361319</v>
+        <v>0.1555292424306624</v>
       </c>
       <c r="C59">
-        <v>369.8599011442325</v>
+        <v>-162.029075952627</v>
       </c>
       <c r="D59">
-        <v>1591.256901144233</v>
+        <v>1104.388924047374</v>
       </c>
       <c r="E59">
-        <v>1977.397000000001</v>
+        <v>2022.418000000001</v>
       </c>
       <c r="F59">
-        <v>2566.197000000001</v>
+        <v>2611.218000000001</v>
       </c>
       <c r="G59">
         <v>1344.8</v>
@@ -6119,45 +6119,45 @@
         <v>304.6</v>
       </c>
       <c r="M59">
-        <v>376.7177196000001</v>
+        <v>524.3325744000001</v>
       </c>
       <c r="N59">
-        <v>-72.1177196000001</v>
+        <v>-219.7325744000001</v>
       </c>
       <c r="O59">
-        <v>-18.02942990000003</v>
+        <v>-54.93314360000002</v>
       </c>
       <c r="P59">
-        <v>-54.08828970000008</v>
+        <v>-164.7994308000001</v>
       </c>
       <c r="Q59">
-        <v>65.11171029999991</v>
+        <v>-45.59943080000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1283589034997256</v>
+        <v>0.1332846935700297</v>
       </c>
       <c r="T59">
-        <v>1.654782589841655</v>
+        <v>1.753513451130059</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.2021407436869608</v>
+        <v>0.1452322508994207</v>
       </c>
       <c r="W59">
-        <v>0.1171257388267542</v>
+        <v>0.1716373640193963</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8085629747478433</v>
+        <v>0.580929003597683</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1555292424306623</v>
+        <v>0.1570792424306623</v>
       </c>
       <c r="C60">
-        <v>-162.029075952626</v>
+        <v>-222.4330242445326</v>
       </c>
       <c r="D60">
-        <v>1104.388924047374</v>
+        <v>1089.005975755467</v>
       </c>
       <c r="E60">
-        <v>2022.418</v>
+        <v>2067.439</v>
       </c>
       <c r="F60">
-        <v>2611.218</v>
+        <v>2656.239</v>
       </c>
       <c r="G60">
         <v>1344.8</v>
@@ -6201,37 +6201,37 @@
         <v>304.6</v>
       </c>
       <c r="M60">
-        <v>524.3325744</v>
+        <v>533.3727912000001</v>
       </c>
       <c r="N60">
-        <v>-219.7325744</v>
+        <v>-228.7727912</v>
       </c>
       <c r="O60">
-        <v>-54.93314359999999</v>
+        <v>-57.19319780000001</v>
       </c>
       <c r="P60">
-        <v>-164.7994308</v>
+        <v>-171.5795934</v>
       </c>
       <c r="Q60">
-        <v>-45.59943079999999</v>
+        <v>-52.37959340000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1332846935700297</v>
+        <v>0.1354184665839328</v>
       </c>
       <c r="T60">
-        <v>1.753513451130058</v>
+        <v>1.796282071889328</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1452322508994208</v>
+        <v>0.1427706873248543</v>
       </c>
       <c r="W60">
-        <v>0.1716373640193963</v>
+        <v>0.1721316459851693</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5809290035976831</v>
+        <v>0.5710827492994173</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1570792424306623</v>
+        <v>0.1586292424306623</v>
       </c>
       <c r="C61">
-        <v>-222.4330242445326</v>
+        <v>-282.4143237737821</v>
       </c>
       <c r="D61">
-        <v>1089.005975755467</v>
+        <v>1074.045676226218</v>
       </c>
       <c r="E61">
-        <v>2067.439</v>
+        <v>2112.46</v>
       </c>
       <c r="F61">
-        <v>2656.239</v>
+        <v>2701.26</v>
       </c>
       <c r="G61">
         <v>1344.8</v>
@@ -6283,37 +6283,37 @@
         <v>304.6</v>
       </c>
       <c r="M61">
-        <v>533.3727912000001</v>
+        <v>542.4130080000001</v>
       </c>
       <c r="N61">
-        <v>-228.7727912</v>
+        <v>-237.8130080000001</v>
       </c>
       <c r="O61">
-        <v>-57.19319780000001</v>
+        <v>-59.45325200000002</v>
       </c>
       <c r="P61">
-        <v>-171.5795934</v>
+        <v>-178.3597560000001</v>
       </c>
       <c r="Q61">
-        <v>-52.37959340000003</v>
+        <v>-59.15975600000007</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1354184665839328</v>
+        <v>0.1376589282485312</v>
       </c>
       <c r="T61">
-        <v>1.796282071889328</v>
+        <v>1.841189123686561</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1427706873248543</v>
+        <v>0.1403911758694401</v>
       </c>
       <c r="W61">
-        <v>0.1721316459851693</v>
+        <v>0.1726094518854164</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5710827492994173</v>
+        <v>0.5615647034777602</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1586292424306623</v>
+        <v>0.1601792424306623</v>
       </c>
       <c r="C62">
-        <v>-282.4143237737821</v>
+        <v>-341.9901570002721</v>
       </c>
       <c r="D62">
-        <v>1074.045676226218</v>
+        <v>1059.490842999728</v>
       </c>
       <c r="E62">
-        <v>2112.46</v>
+        <v>2157.481</v>
       </c>
       <c r="F62">
-        <v>2701.26</v>
+        <v>2746.281</v>
       </c>
       <c r="G62">
         <v>1344.8</v>
@@ -6365,37 +6365,37 @@
         <v>304.6</v>
       </c>
       <c r="M62">
-        <v>542.4130080000001</v>
+        <v>551.4532248</v>
       </c>
       <c r="N62">
-        <v>-237.8130080000001</v>
+        <v>-246.8532248</v>
       </c>
       <c r="O62">
-        <v>-59.45325200000002</v>
+        <v>-61.71330620000001</v>
       </c>
       <c r="P62">
-        <v>-178.3597560000001</v>
+        <v>-185.1399186</v>
       </c>
       <c r="Q62">
-        <v>-59.15975600000007</v>
+        <v>-65.93991860000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1376589282485312</v>
+        <v>0.1400142853831089</v>
       </c>
       <c r="T62">
-        <v>1.841189123686561</v>
+        <v>1.888399101216985</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1403911758694401</v>
+        <v>0.1380896811830558</v>
       </c>
       <c r="W62">
-        <v>0.1726094518854164</v>
+        <v>0.1730715920184424</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5615647034777602</v>
+        <v>0.5523587247322232</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1601792424306623</v>
+        <v>0.1617292424306623</v>
       </c>
       <c r="C63">
-        <v>-341.9901570002721</v>
+        <v>-401.1767874505172</v>
       </c>
       <c r="D63">
-        <v>1059.490842999728</v>
+        <v>1045.325212549483</v>
       </c>
       <c r="E63">
-        <v>2157.481</v>
+        <v>2202.502</v>
       </c>
       <c r="F63">
-        <v>2746.281</v>
+        <v>2791.302</v>
       </c>
       <c r="G63">
         <v>1344.8</v>
@@ -6447,37 +6447,37 @@
         <v>304.6</v>
       </c>
       <c r="M63">
-        <v>551.4532248</v>
+        <v>560.4934416000001</v>
       </c>
       <c r="N63">
-        <v>-246.8532248</v>
+        <v>-255.8934416000001</v>
       </c>
       <c r="O63">
-        <v>-61.71330620000001</v>
+        <v>-63.97336040000002</v>
       </c>
       <c r="P63">
-        <v>-185.1399186</v>
+        <v>-191.9200812000001</v>
       </c>
       <c r="Q63">
-        <v>-65.93991860000003</v>
+        <v>-72.72008120000007</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1400142853831089</v>
+        <v>0.1424936086826644</v>
       </c>
       <c r="T63">
-        <v>1.888399101216985</v>
+        <v>1.938093814406906</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1380896811830558</v>
+        <v>0.1358624282607484</v>
       </c>
       <c r="W63">
-        <v>0.1730715920184424</v>
+        <v>0.1735188244052417</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5523587247322232</v>
+        <v>0.5434497130429937</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1617292424306623</v>
+        <v>0.1632792424306623</v>
       </c>
       <c r="C64">
-        <v>-401.1767874505172</v>
+        <v>-459.9896203388507</v>
       </c>
       <c r="D64">
-        <v>1045.325212549483</v>
+        <v>1031.53337966115</v>
       </c>
       <c r="E64">
-        <v>2202.502</v>
+        <v>2247.523</v>
       </c>
       <c r="F64">
-        <v>2791.302</v>
+        <v>2836.323</v>
       </c>
       <c r="G64">
         <v>1344.8</v>
@@ -6529,37 +6529,37 @@
         <v>304.6</v>
       </c>
       <c r="M64">
-        <v>560.4934416000001</v>
+        <v>569.5336584</v>
       </c>
       <c r="N64">
-        <v>-255.8934416000001</v>
+        <v>-264.9336584</v>
       </c>
       <c r="O64">
-        <v>-63.97336040000002</v>
+        <v>-66.2334146</v>
       </c>
       <c r="P64">
-        <v>-191.9200812000001</v>
+        <v>-198.7002438</v>
       </c>
       <c r="Q64">
-        <v>-72.72008120000007</v>
+        <v>-79.50024380000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1424936086826644</v>
+        <v>0.1451069494578715</v>
       </c>
       <c r="T64">
-        <v>1.938093814406906</v>
+        <v>1.990474728309796</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1358624282607484</v>
+        <v>0.1337058817804191</v>
       </c>
       <c r="W64">
-        <v>0.1735188244052417</v>
+        <v>0.1739518589384919</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5434497130429937</v>
+        <v>0.5348235271216764</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1632792424306623</v>
+        <v>0.1648292424306623</v>
       </c>
       <c r="C65">
-        <v>-459.9896203388507</v>
+        <v>-518.4432584521801</v>
       </c>
       <c r="D65">
-        <v>1031.53337966115</v>
+        <v>1018.10074154782</v>
       </c>
       <c r="E65">
-        <v>2247.523</v>
+        <v>2292.544000000001</v>
       </c>
       <c r="F65">
-        <v>2836.323</v>
+        <v>2881.344000000001</v>
       </c>
       <c r="G65">
         <v>1344.8</v>
@@ -6611,37 +6611,37 @@
         <v>304.6</v>
       </c>
       <c r="M65">
-        <v>569.5336584</v>
+        <v>578.5738752000001</v>
       </c>
       <c r="N65">
-        <v>-264.9336584</v>
+        <v>-273.9738752000001</v>
       </c>
       <c r="O65">
-        <v>-66.2334146</v>
+        <v>-68.49346880000002</v>
       </c>
       <c r="P65">
-        <v>-198.7002438</v>
+        <v>-205.4804064</v>
       </c>
       <c r="Q65">
-        <v>-79.50024380000002</v>
+        <v>-86.28040640000006</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1451069494578715</v>
+        <v>0.1478654758317013</v>
       </c>
       <c r="T65">
-        <v>1.990474728309796</v>
+        <v>2.045765692985068</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1337058817804191</v>
+        <v>0.1316167273776001</v>
       </c>
       <c r="W65">
-        <v>0.1739518589384919</v>
+        <v>0.1743713611425779</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5348235271216764</v>
+        <v>0.5264669095104002</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1648292424306623</v>
+        <v>0.1663792424306623</v>
       </c>
       <c r="C66">
-        <v>-518.4432584521801</v>
+        <v>-576.5515537244696</v>
       </c>
       <c r="D66">
-        <v>1018.10074154782</v>
+        <v>1005.013446275531</v>
       </c>
       <c r="E66">
-        <v>2292.544000000001</v>
+        <v>2337.565000000001</v>
       </c>
       <c r="F66">
-        <v>2881.344000000001</v>
+        <v>2926.365</v>
       </c>
       <c r="G66">
         <v>1344.8</v>
@@ -6693,37 +6693,37 @@
         <v>304.6</v>
       </c>
       <c r="M66">
-        <v>578.5738752000001</v>
+        <v>587.614092</v>
       </c>
       <c r="N66">
-        <v>-273.9738752000001</v>
+        <v>-283.014092</v>
       </c>
       <c r="O66">
-        <v>-68.49346880000002</v>
+        <v>-70.753523</v>
       </c>
       <c r="P66">
-        <v>-205.4804064</v>
+        <v>-212.260569</v>
       </c>
       <c r="Q66">
-        <v>-86.28040640000006</v>
+        <v>-93.06056900000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1478654758317013</v>
+        <v>0.1507816322840356</v>
       </c>
       <c r="T66">
-        <v>2.045765692985068</v>
+        <v>2.10421614135607</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1316167273776001</v>
+        <v>0.1295918546487139</v>
       </c>
       <c r="W66">
-        <v>0.1743713611425779</v>
+        <v>0.1747779555865382</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5264669095104002</v>
+        <v>0.5183674185948557</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1663792424306623</v>
+        <v>0.1679292424306623</v>
       </c>
       <c r="C67">
-        <v>-576.5515537244696</v>
+        <v>-634.3276548838949</v>
       </c>
       <c r="D67">
-        <v>1005.013446275531</v>
+        <v>992.2583451161054</v>
       </c>
       <c r="E67">
-        <v>2337.565000000001</v>
+        <v>2382.586</v>
       </c>
       <c r="F67">
-        <v>2926.365</v>
+        <v>2971.386</v>
       </c>
       <c r="G67">
         <v>1344.8</v>
@@ -6775,37 +6775,37 @@
         <v>304.6</v>
       </c>
       <c r="M67">
-        <v>587.614092</v>
+        <v>596.6543088000001</v>
       </c>
       <c r="N67">
-        <v>-283.014092</v>
+        <v>-292.0543088000001</v>
       </c>
       <c r="O67">
-        <v>-70.753523</v>
+        <v>-73.01357720000001</v>
       </c>
       <c r="P67">
-        <v>-212.260569</v>
+        <v>-219.0407316</v>
       </c>
       <c r="Q67">
-        <v>-93.06056900000002</v>
+        <v>-99.84073160000005</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1507816322840356</v>
+        <v>0.1538693273512131</v>
       </c>
       <c r="T67">
-        <v>2.10421614135607</v>
+        <v>2.166104851395954</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1295918546487139</v>
+        <v>0.127628341699491</v>
       </c>
       <c r="W67">
-        <v>0.1747779555865382</v>
+        <v>0.1751722289867422</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5183674185948557</v>
+        <v>0.5105133667979638</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1679292424306623</v>
+        <v>0.1694792424306624</v>
       </c>
       <c r="C68">
-        <v>-634.3276548838949</v>
+        <v>-691.7840515171847</v>
       </c>
       <c r="D68">
-        <v>992.2583451161054</v>
+        <v>979.8229484828159</v>
       </c>
       <c r="E68">
-        <v>2382.586</v>
+        <v>2427.607000000001</v>
       </c>
       <c r="F68">
-        <v>2971.386</v>
+        <v>3016.407000000001</v>
       </c>
       <c r="G68">
         <v>1344.8</v>
@@ -6857,37 +6857,37 @@
         <v>304.6</v>
       </c>
       <c r="M68">
-        <v>596.6543088000001</v>
+        <v>605.6945256000001</v>
       </c>
       <c r="N68">
-        <v>-292.0543088000001</v>
+        <v>-301.0945256000001</v>
       </c>
       <c r="O68">
-        <v>-73.01357720000001</v>
+        <v>-75.27363140000003</v>
       </c>
       <c r="P68">
-        <v>-219.0407316</v>
+        <v>-225.8208942000001</v>
       </c>
       <c r="Q68">
-        <v>-99.84073160000005</v>
+        <v>-106.6208942000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1538693273512131</v>
+        <v>0.1571441554527651</v>
       </c>
       <c r="T68">
-        <v>2.166104851395954</v>
+        <v>2.231744392347347</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.127628341699491</v>
+        <v>0.1257234410771105</v>
       </c>
       <c r="W68">
-        <v>0.1751722289867422</v>
+        <v>0.1755547330317162</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5105133667979638</v>
+        <v>0.5028937643084419</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1694792424306624</v>
+        <v>0.195330905914963</v>
       </c>
       <c r="C69">
-        <v>-691.7840515171847</v>
+        <v>-906.201825939042</v>
       </c>
       <c r="D69">
-        <v>979.8229484828159</v>
+        <v>810.4261740609586</v>
       </c>
       <c r="E69">
-        <v>2427.607000000001</v>
+        <v>2472.628000000001</v>
       </c>
       <c r="F69">
-        <v>3016.407000000001</v>
+        <v>3061.428</v>
       </c>
       <c r="G69">
         <v>1344.8</v>
@@ -6939,45 +6939,45 @@
         <v>304.6</v>
       </c>
       <c r="M69">
-        <v>605.6945256000001</v>
+        <v>721.8847224000001</v>
       </c>
       <c r="N69">
-        <v>-301.0945256000001</v>
+        <v>-417.2847224000001</v>
       </c>
       <c r="O69">
-        <v>-75.27363140000003</v>
+        <v>-104.3211806</v>
       </c>
       <c r="P69">
-        <v>-225.8208942000001</v>
+        <v>-312.9635418</v>
       </c>
       <c r="Q69">
-        <v>-106.6208942000001</v>
+        <v>-193.7635418</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1571441554527651</v>
+        <v>0.1621913586991036</v>
       </c>
       <c r="T69">
-        <v>2.231744392347347</v>
+        <v>2.332908818052941</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1257234410771105</v>
+        <v>0.1054877567526701</v>
       </c>
       <c r="W69">
-        <v>0.1755547330317162</v>
+        <v>0.2109259869577204</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5028937643084419</v>
+        <v>0.4219510270106804</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.195330905914963</v>
+        <v>0.197230905914963</v>
       </c>
       <c r="C70">
-        <v>-906.201825939042</v>
+        <v>-961.3912240042328</v>
       </c>
       <c r="D70">
-        <v>810.4261740609586</v>
+        <v>800.2577759957677</v>
       </c>
       <c r="E70">
-        <v>2472.628000000001</v>
+        <v>2517.649</v>
       </c>
       <c r="F70">
-        <v>3061.428</v>
+        <v>3106.449000000001</v>
       </c>
       <c r="G70">
         <v>1344.8</v>
@@ -7021,37 +7021,37 @@
         <v>304.6</v>
       </c>
       <c r="M70">
-        <v>721.8847224000001</v>
+        <v>732.5006742000002</v>
       </c>
       <c r="N70">
-        <v>-417.2847224000001</v>
+        <v>-427.9006742000001</v>
       </c>
       <c r="O70">
-        <v>-104.3211806</v>
+        <v>-106.97516855</v>
       </c>
       <c r="P70">
-        <v>-312.9635418</v>
+        <v>-320.9255056500001</v>
       </c>
       <c r="Q70">
-        <v>-193.7635418</v>
+        <v>-201.7255056500001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1621913586991036</v>
+        <v>0.1659459186571392</v>
       </c>
       <c r="T70">
-        <v>2.332908818052941</v>
+        <v>2.408163941215939</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1054877567526701</v>
+        <v>0.1039589486837908</v>
       </c>
       <c r="W70">
-        <v>0.2109259869577204</v>
+        <v>0.2112864799003621</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4219510270106804</v>
+        <v>0.4158357947351633</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.197230905914963</v>
+        <v>0.199130905914963</v>
       </c>
       <c r="C71">
-        <v>-961.3912240042328</v>
+        <v>-1016.328618649649</v>
       </c>
       <c r="D71">
-        <v>800.2577759957677</v>
+        <v>790.3413813503512</v>
       </c>
       <c r="E71">
-        <v>2517.649</v>
+        <v>2562.670000000001</v>
       </c>
       <c r="F71">
-        <v>3106.449000000001</v>
+        <v>3151.470000000001</v>
       </c>
       <c r="G71">
         <v>1344.8</v>
@@ -7103,37 +7103,37 @@
         <v>304.6</v>
       </c>
       <c r="M71">
-        <v>732.5006742000002</v>
+        <v>743.1166260000002</v>
       </c>
       <c r="N71">
-        <v>-427.9006742000001</v>
+        <v>-438.5166260000002</v>
       </c>
       <c r="O71">
-        <v>-106.97516855</v>
+        <v>-109.6291565000001</v>
       </c>
       <c r="P71">
-        <v>-320.9255056500001</v>
+        <v>-328.8874695000002</v>
       </c>
       <c r="Q71">
-        <v>-201.7255056500001</v>
+        <v>-209.6874695000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1659459186571392</v>
+        <v>0.1699507826123772</v>
       </c>
       <c r="T71">
-        <v>2.408163941215939</v>
+        <v>2.488436072589804</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1039589486837908</v>
+        <v>0.102473820845451</v>
       </c>
       <c r="W71">
-        <v>0.2112864799003621</v>
+        <v>0.2116366730446427</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4158357947351633</v>
+        <v>0.4098952833818038</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.199130905914963</v>
+        <v>0.201030905914963</v>
       </c>
       <c r="C72">
-        <v>-1016.328618649649</v>
+        <v>-1071.023263312834</v>
       </c>
       <c r="D72">
-        <v>790.3413813503512</v>
+        <v>780.6677366871662</v>
       </c>
       <c r="E72">
-        <v>2562.670000000001</v>
+        <v>2607.691000000001</v>
       </c>
       <c r="F72">
-        <v>3151.470000000001</v>
+        <v>3196.491</v>
       </c>
       <c r="G72">
         <v>1344.8</v>
@@ -7185,37 +7185,37 @@
         <v>304.6</v>
       </c>
       <c r="M72">
-        <v>743.1166260000002</v>
+        <v>753.7325778000002</v>
       </c>
       <c r="N72">
-        <v>-438.5166260000002</v>
+        <v>-449.1325778000001</v>
       </c>
       <c r="O72">
-        <v>-109.6291565000001</v>
+        <v>-112.28314445</v>
       </c>
       <c r="P72">
-        <v>-328.8874695000002</v>
+        <v>-336.8494333500001</v>
       </c>
       <c r="Q72">
-        <v>-209.6874695000002</v>
+        <v>-217.6494333500002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1699507826123772</v>
+        <v>0.1742318440817695</v>
       </c>
       <c r="T72">
-        <v>2.488436072589804</v>
+        <v>2.574244213023935</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.102473820845451</v>
+        <v>0.1010305275941066</v>
       </c>
       <c r="W72">
-        <v>0.2116366730446427</v>
+        <v>0.2119770015933097</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4098952833818038</v>
+        <v>0.4041221103764263</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.201030905914963</v>
+        <v>0.202930905914963</v>
       </c>
       <c r="C73">
-        <v>-1071.023263312834</v>
+        <v>-1125.483963867404</v>
       </c>
       <c r="D73">
-        <v>780.6677366871662</v>
+        <v>771.2280361325957</v>
       </c>
       <c r="E73">
-        <v>2607.691</v>
+        <v>2652.712</v>
       </c>
       <c r="F73">
-        <v>3196.491</v>
+        <v>3241.512</v>
       </c>
       <c r="G73">
         <v>1344.8</v>
@@ -7267,37 +7267,37 @@
         <v>304.6</v>
       </c>
       <c r="M73">
-        <v>753.7325778000001</v>
+        <v>764.3485296000001</v>
       </c>
       <c r="N73">
-        <v>-449.1325778</v>
+        <v>-459.7485296000001</v>
       </c>
       <c r="O73">
-        <v>-112.28314445</v>
+        <v>-114.9371324</v>
       </c>
       <c r="P73">
-        <v>-336.84943335</v>
+        <v>-344.8113972000001</v>
       </c>
       <c r="Q73">
-        <v>-217.64943335</v>
+        <v>-225.6113972000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1742318440817695</v>
+        <v>0.1788186956561184</v>
       </c>
       <c r="T73">
-        <v>2.574244213023934</v>
+        <v>2.666181506346218</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1010305275941066</v>
+        <v>0.09962732582196622</v>
       </c>
       <c r="W73">
-        <v>0.2119770015933097</v>
+        <v>0.2123078765711804</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4041221103764264</v>
+        <v>0.3985093032878649</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.202930905914963</v>
+        <v>0.204830905914963</v>
       </c>
       <c r="C74">
-        <v>-1125.483963867404</v>
+        <v>-1179.719105359093</v>
       </c>
       <c r="D74">
-        <v>771.2280361325957</v>
+        <v>762.013894640907</v>
       </c>
       <c r="E74">
-        <v>2652.712</v>
+        <v>2697.733</v>
       </c>
       <c r="F74">
-        <v>3241.512</v>
+        <v>3286.533</v>
       </c>
       <c r="G74">
         <v>1344.8</v>
@@ -7349,37 +7349,37 @@
         <v>304.6</v>
       </c>
       <c r="M74">
-        <v>764.3485296000001</v>
+        <v>774.9644814000001</v>
       </c>
       <c r="N74">
-        <v>-459.7485296000001</v>
+        <v>-470.3644814</v>
       </c>
       <c r="O74">
-        <v>-114.9371324</v>
+        <v>-117.59112035</v>
       </c>
       <c r="P74">
-        <v>-344.8113972000001</v>
+        <v>-352.7733610500001</v>
       </c>
       <c r="Q74">
-        <v>-225.6113972000001</v>
+        <v>-233.5733610500001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1788186956561184</v>
+        <v>0.1837453140137524</v>
       </c>
       <c r="T74">
-        <v>2.666181506346218</v>
+        <v>2.764928969544226</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09962732582196622</v>
+        <v>0.09826256793399409</v>
       </c>
       <c r="W74">
-        <v>0.2123078765711804</v>
+        <v>0.2126296864811642</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3985093032878649</v>
+        <v>0.3930502717359764</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.204830905914963</v>
+        <v>0.206730905914963</v>
       </c>
       <c r="C75">
-        <v>-1179.719105359093</v>
+        <v>-1233.736676847871</v>
       </c>
       <c r="D75">
-        <v>762.013894640907</v>
+        <v>753.0173231521292</v>
       </c>
       <c r="E75">
-        <v>2697.733</v>
+        <v>2742.754</v>
       </c>
       <c r="F75">
-        <v>3286.533</v>
+        <v>3331.554</v>
       </c>
       <c r="G75">
         <v>1344.8</v>
@@ -7431,37 +7431,37 @@
         <v>304.6</v>
       </c>
       <c r="M75">
-        <v>774.9644814000001</v>
+        <v>785.5804332</v>
       </c>
       <c r="N75">
-        <v>-470.3644814</v>
+        <v>-480.9804332</v>
       </c>
       <c r="O75">
-        <v>-117.59112035</v>
+        <v>-120.2451083</v>
       </c>
       <c r="P75">
-        <v>-352.7733610500001</v>
+        <v>-360.7353249</v>
       </c>
       <c r="Q75">
-        <v>-233.5733610500001</v>
+        <v>-241.5353249</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1837453140137524</v>
+        <v>0.1890509030142813</v>
       </c>
       <c r="T75">
-        <v>2.764928969544226</v>
+        <v>2.871272391449773</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09826256793399409</v>
+        <v>0.09693469539434553</v>
       </c>
       <c r="W75">
-        <v>0.2126296864811642</v>
+        <v>0.2129427988260133</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3930502717359764</v>
+        <v>0.3877387815773821</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.206730905914963</v>
+        <v>0.208630905914963</v>
       </c>
       <c r="C76">
-        <v>-1233.736676847871</v>
+        <v>-1287.544294510837</v>
       </c>
       <c r="D76">
-        <v>753.0173231521292</v>
+        <v>744.2307054891639</v>
       </c>
       <c r="E76">
-        <v>2742.754</v>
+        <v>2787.775000000001</v>
       </c>
       <c r="F76">
-        <v>3331.554</v>
+        <v>3376.575</v>
       </c>
       <c r="G76">
         <v>1344.8</v>
@@ -7513,37 +7513,37 @@
         <v>304.6</v>
       </c>
       <c r="M76">
-        <v>785.5804332</v>
+        <v>796.1963850000001</v>
       </c>
       <c r="N76">
-        <v>-480.9804332</v>
+        <v>-491.5963850000001</v>
       </c>
       <c r="O76">
-        <v>-120.2451083</v>
+        <v>-122.89909625</v>
       </c>
       <c r="P76">
-        <v>-360.7353249</v>
+        <v>-368.69728875</v>
       </c>
       <c r="Q76">
-        <v>-241.5353249</v>
+        <v>-249.4972887500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1890509030142813</v>
+        <v>0.1947809391348526</v>
       </c>
       <c r="T76">
-        <v>2.871272391449773</v>
+        <v>2.986123287107764</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09693469539434553</v>
+        <v>0.09564223278908758</v>
       </c>
       <c r="W76">
-        <v>0.2129427988260133</v>
+        <v>0.2132475615083332</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3877387815773821</v>
+        <v>0.3825689311563503</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.208630905914963</v>
+        <v>0.210530905914963</v>
       </c>
       <c r="C77">
-        <v>-1287.544294510837</v>
+        <v>-1341.149223146301</v>
       </c>
       <c r="D77">
-        <v>744.2307054891639</v>
+        <v>735.6467768536995</v>
       </c>
       <c r="E77">
-        <v>2787.775000000001</v>
+        <v>2832.796</v>
       </c>
       <c r="F77">
-        <v>3376.575</v>
+        <v>3421.596</v>
       </c>
       <c r="G77">
         <v>1344.8</v>
@@ -7595,37 +7595,37 @@
         <v>304.6</v>
       </c>
       <c r="M77">
-        <v>796.1963850000001</v>
+        <v>806.8123368000001</v>
       </c>
       <c r="N77">
-        <v>-491.5963850000001</v>
+        <v>-502.2123368000001</v>
       </c>
       <c r="O77">
-        <v>-122.89909625</v>
+        <v>-125.5530842</v>
       </c>
       <c r="P77">
-        <v>-368.69728875</v>
+        <v>-376.6592526000001</v>
       </c>
       <c r="Q77">
-        <v>-249.4972887500001</v>
+        <v>-257.4592526000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1947809391348526</v>
+        <v>0.2009884782654715</v>
       </c>
       <c r="T77">
-        <v>2.986123287107764</v>
+        <v>3.110545090737254</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09564223278908758</v>
+        <v>0.09438378235765221</v>
       </c>
       <c r="W77">
-        <v>0.2132475615083332</v>
+        <v>0.2135443041200656</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3825689311563503</v>
+        <v>0.3775351294306089</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.210530905914963</v>
+        <v>0.212430905914963</v>
       </c>
       <c r="C78">
-        <v>-1341.149223146301</v>
+        <v>-1394.558396206677</v>
       </c>
       <c r="D78">
-        <v>735.6467768536995</v>
+        <v>727.2586037933233</v>
       </c>
       <c r="E78">
-        <v>2832.796</v>
+        <v>2877.817</v>
       </c>
       <c r="F78">
-        <v>3421.596</v>
+        <v>3466.617</v>
       </c>
       <c r="G78">
         <v>1344.8</v>
@@ -7677,37 +7677,37 @@
         <v>304.6</v>
       </c>
       <c r="M78">
-        <v>806.8123368000001</v>
+        <v>817.4282886000001</v>
       </c>
       <c r="N78">
-        <v>-502.2123368000001</v>
+        <v>-512.8282886000001</v>
       </c>
       <c r="O78">
-        <v>-125.5530842</v>
+        <v>-128.20707215</v>
       </c>
       <c r="P78">
-        <v>-376.6592526000001</v>
+        <v>-384.62121645</v>
       </c>
       <c r="Q78">
-        <v>-257.4592526000001</v>
+        <v>-265.42121645</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2009884782654715</v>
+        <v>0.2077358034074485</v>
       </c>
       <c r="T78">
-        <v>3.110545090737254</v>
+        <v>3.245786181638874</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09438378235765221</v>
+        <v>0.09315801895040998</v>
       </c>
       <c r="W78">
-        <v>0.2135443041200656</v>
+        <v>0.2138333391314933</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3775351294306089</v>
+        <v>0.3726320758016399</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.212430905914963</v>
+        <v>0.214330905914963</v>
       </c>
       <c r="C79">
-        <v>-1394.558396206677</v>
+        <v>-1447.778434476278</v>
       </c>
       <c r="D79">
-        <v>727.2586037933233</v>
+        <v>719.0595655237223</v>
       </c>
       <c r="E79">
-        <v>2877.817</v>
+        <v>2922.838000000001</v>
       </c>
       <c r="F79">
-        <v>3466.617</v>
+        <v>3511.638</v>
       </c>
       <c r="G79">
         <v>1344.8</v>
@@ -7759,37 +7759,37 @@
         <v>304.6</v>
       </c>
       <c r="M79">
-        <v>817.4282886000001</v>
+        <v>828.0442404000001</v>
       </c>
       <c r="N79">
-        <v>-512.8282886000001</v>
+        <v>-523.4442404000001</v>
       </c>
       <c r="O79">
-        <v>-128.20707215</v>
+        <v>-130.8610601</v>
       </c>
       <c r="P79">
-        <v>-384.62121645</v>
+        <v>-392.5831803000001</v>
       </c>
       <c r="Q79">
-        <v>-265.42121645</v>
+        <v>-273.3831803000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2077358034074485</v>
+        <v>0.2150965217441507</v>
       </c>
       <c r="T79">
-        <v>3.245786181638874</v>
+        <v>3.393321917167914</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09315801895040998</v>
+        <v>0.09196368537412267</v>
       </c>
       <c r="W79">
-        <v>0.2138333391314933</v>
+        <v>0.2141149629887819</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3726320758016399</v>
+        <v>0.3678547414964907</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.214330905914963</v>
+        <v>0.2162309059149631</v>
       </c>
       <c r="C80">
-        <v>-1447.778434476278</v>
+        <v>-1500.815663499768</v>
       </c>
       <c r="D80">
-        <v>719.0595655237223</v>
+        <v>711.0433365002332</v>
       </c>
       <c r="E80">
-        <v>2922.838000000001</v>
+        <v>2967.859</v>
       </c>
       <c r="F80">
-        <v>3511.638</v>
+        <v>3556.659000000001</v>
       </c>
       <c r="G80">
         <v>1344.8</v>
@@ -7841,37 +7841,37 @@
         <v>304.6</v>
       </c>
       <c r="M80">
-        <v>828.0442404000001</v>
+        <v>838.6601922000002</v>
       </c>
       <c r="N80">
-        <v>-523.4442404000001</v>
+        <v>-534.0601922000002</v>
       </c>
       <c r="O80">
-        <v>-130.8610601</v>
+        <v>-133.51504805</v>
       </c>
       <c r="P80">
-        <v>-392.5831803000001</v>
+        <v>-400.5451441500002</v>
       </c>
       <c r="Q80">
-        <v>-273.3831803000001</v>
+        <v>-281.3451441500002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2150965217441507</v>
+        <v>0.2231582608748245</v>
       </c>
       <c r="T80">
-        <v>3.393321917167914</v>
+        <v>3.554908675128291</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09196368537412267</v>
+        <v>0.09079958809090592</v>
       </c>
       <c r="W80">
-        <v>0.2141149629887819</v>
+        <v>0.2143894571281644</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3678547414964907</v>
+        <v>0.3631983523636236</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2162309059149631</v>
+        <v>0.218130905914963</v>
       </c>
       <c r="C81">
-        <v>-1500.815663499768</v>
+        <v>-1553.676129857688</v>
       </c>
       <c r="D81">
-        <v>711.0433365002332</v>
+        <v>703.2038701423118</v>
       </c>
       <c r="E81">
-        <v>2967.859</v>
+        <v>3012.88</v>
       </c>
       <c r="F81">
-        <v>3556.659000000001</v>
+        <v>3601.68</v>
       </c>
       <c r="G81">
         <v>1344.8</v>
@@ -7923,37 +7923,37 @@
         <v>304.6</v>
       </c>
       <c r="M81">
-        <v>838.6601922000002</v>
+        <v>849.2761440000002</v>
       </c>
       <c r="N81">
-        <v>-534.0601922000002</v>
+        <v>-544.6761440000001</v>
       </c>
       <c r="O81">
-        <v>-133.51504805</v>
+        <v>-136.169036</v>
       </c>
       <c r="P81">
-        <v>-400.5451441500002</v>
+        <v>-408.5071080000001</v>
       </c>
       <c r="Q81">
-        <v>-281.3451441500002</v>
+        <v>-289.3071080000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2231582608748245</v>
+        <v>0.2320261739185658</v>
       </c>
       <c r="T81">
-        <v>3.554908675128291</v>
+        <v>3.732654108884706</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09079958809090592</v>
+        <v>0.08966459323976959</v>
       </c>
       <c r="W81">
-        <v>0.2143894571281644</v>
+        <v>0.2146570889140623</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3631983523636236</v>
+        <v>0.3586583729590784</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.218130905914963</v>
+        <v>0.220030905914963</v>
       </c>
       <c r="C82">
-        <v>-1553.676129857688</v>
+        <v>-1606.365616377081</v>
       </c>
       <c r="D82">
-        <v>703.2038701423118</v>
+        <v>695.5353836229197</v>
       </c>
       <c r="E82">
-        <v>3012.88</v>
+        <v>3057.901000000001</v>
       </c>
       <c r="F82">
-        <v>3601.68</v>
+        <v>3646.701</v>
       </c>
       <c r="G82">
         <v>1344.8</v>
@@ -8005,37 +8005,37 @@
         <v>304.6</v>
       </c>
       <c r="M82">
-        <v>849.2761440000002</v>
+        <v>859.8920958000001</v>
       </c>
       <c r="N82">
-        <v>-544.6761440000001</v>
+        <v>-555.2920958000001</v>
       </c>
       <c r="O82">
-        <v>-136.169036</v>
+        <v>-138.82302395</v>
       </c>
       <c r="P82">
-        <v>-408.5071080000001</v>
+        <v>-416.4690718500001</v>
       </c>
       <c r="Q82">
-        <v>-289.3071080000001</v>
+        <v>-297.2690718500001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2320261739185658</v>
+        <v>0.2418275514932272</v>
       </c>
       <c r="T82">
-        <v>3.732654108884706</v>
+        <v>3.92910958829969</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08966459323976959</v>
+        <v>0.08855762295285886</v>
       </c>
       <c r="W82">
-        <v>0.2146570889140623</v>
+        <v>0.2149181125077159</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3586583729590784</v>
+        <v>0.3542304918114355</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.220030905914963</v>
+        <v>0.221930905914963</v>
       </c>
       <c r="C83">
-        <v>-1606.365616377081</v>
+        <v>-1658.889656357592</v>
       </c>
       <c r="D83">
-        <v>695.5353836229197</v>
+        <v>688.0323436424087</v>
       </c>
       <c r="E83">
-        <v>3057.901000000001</v>
+        <v>3102.922</v>
       </c>
       <c r="F83">
-        <v>3646.701</v>
+        <v>3691.722000000001</v>
       </c>
       <c r="G83">
         <v>1344.8</v>
@@ -8087,37 +8087,37 @@
         <v>304.6</v>
       </c>
       <c r="M83">
-        <v>859.8920958000001</v>
+        <v>870.5080476000002</v>
       </c>
       <c r="N83">
-        <v>-555.2920958000001</v>
+        <v>-565.9080476000001</v>
       </c>
       <c r="O83">
-        <v>-138.82302395</v>
+        <v>-141.4770119</v>
       </c>
       <c r="P83">
-        <v>-416.4690718500001</v>
+        <v>-424.4310357000001</v>
       </c>
       <c r="Q83">
-        <v>-297.2690718500001</v>
+        <v>-305.2310357000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2418275514932272</v>
+        <v>0.2527179710206287</v>
       </c>
       <c r="T83">
-        <v>3.92910958829969</v>
+        <v>4.14739345431634</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08855762295285886</v>
+        <v>0.08747765194123863</v>
       </c>
       <c r="W83">
-        <v>0.2149181125077159</v>
+        <v>0.215172769672256</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3542304918114355</v>
+        <v>0.3499106077649545</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.221930905914963</v>
+        <v>0.223830905914963</v>
       </c>
       <c r="C84">
-        <v>-1658.889656357592</v>
+        <v>-1711.253546886639</v>
       </c>
       <c r="D84">
-        <v>688.0323436424087</v>
+        <v>680.6894531133621</v>
       </c>
       <c r="E84">
-        <v>3102.922</v>
+        <v>3147.943000000001</v>
       </c>
       <c r="F84">
-        <v>3691.722000000001</v>
+        <v>3736.743000000001</v>
       </c>
       <c r="G84">
         <v>1344.8</v>
@@ -8169,37 +8169,37 @@
         <v>304.6</v>
       </c>
       <c r="M84">
-        <v>870.5080476000002</v>
+        <v>881.1239994000002</v>
       </c>
       <c r="N84">
-        <v>-565.9080476000001</v>
+        <v>-576.5239994000002</v>
       </c>
       <c r="O84">
-        <v>-141.4770119</v>
+        <v>-144.1309998500001</v>
       </c>
       <c r="P84">
-        <v>-424.4310357000001</v>
+        <v>-432.3929995500001</v>
       </c>
       <c r="Q84">
-        <v>-305.2310357000001</v>
+        <v>-313.1929995500001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2527179710206287</v>
+        <v>0.2648896163747833</v>
       </c>
       <c r="T84">
-        <v>4.14739345431634</v>
+        <v>4.391357775158478</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08747765194123863</v>
+        <v>0.08642370432748876</v>
       </c>
       <c r="W84">
-        <v>0.215172769672256</v>
+        <v>0.2154212905195781</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3499106077649545</v>
+        <v>0.3456948173099551</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.223830905914963</v>
+        <v>0.225730905914963</v>
       </c>
       <c r="C85">
-        <v>-1711.253546886639</v>
+        <v>-1763.462361310952</v>
       </c>
       <c r="D85">
-        <v>680.6894531133621</v>
+        <v>673.5016386890485</v>
       </c>
       <c r="E85">
-        <v>3147.943000000001</v>
+        <v>3192.964000000001</v>
       </c>
       <c r="F85">
-        <v>3736.743000000001</v>
+        <v>3781.764000000001</v>
       </c>
       <c r="G85">
         <v>1344.8</v>
@@ -8251,37 +8251,37 @@
         <v>304.6</v>
       </c>
       <c r="M85">
-        <v>881.1239994000002</v>
+        <v>891.7399512000002</v>
       </c>
       <c r="N85">
-        <v>-576.5239994000002</v>
+        <v>-587.1399512000002</v>
       </c>
       <c r="O85">
-        <v>-144.1309998500001</v>
+        <v>-146.7849878</v>
       </c>
       <c r="P85">
-        <v>-432.3929995500001</v>
+        <v>-440.3549634000001</v>
       </c>
       <c r="Q85">
-        <v>-313.1929995500001</v>
+        <v>-321.1549634000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2648896163747833</v>
+        <v>0.2785827173982073</v>
       </c>
       <c r="T85">
-        <v>4.391357775158478</v>
+        <v>4.665817636105884</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08642370432748876</v>
+        <v>0.08539485070454247</v>
       </c>
       <c r="W85">
-        <v>0.2154212905195781</v>
+        <v>0.2156638942038689</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3456948173099551</v>
+        <v>0.3415794028181699</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.225730905914963</v>
+        <v>0.227630905914963</v>
       </c>
       <c r="C86">
-        <v>-1763.462361310952</v>
+        <v>-1815.52096092621</v>
       </c>
       <c r="D86">
-        <v>673.5016386890485</v>
+        <v>666.4640390737903</v>
       </c>
       <c r="E86">
-        <v>3192.964</v>
+        <v>3237.985000000001</v>
       </c>
       <c r="F86">
-        <v>3781.764</v>
+        <v>3826.785</v>
       </c>
       <c r="G86">
         <v>1344.8</v>
@@ -8333,37 +8333,37 @@
         <v>304.6</v>
       </c>
       <c r="M86">
-        <v>891.7399512000001</v>
+        <v>902.3559030000001</v>
       </c>
       <c r="N86">
-        <v>-587.1399512</v>
+        <v>-597.7559030000001</v>
       </c>
       <c r="O86">
-        <v>-146.7849878</v>
+        <v>-149.43897575</v>
       </c>
       <c r="P86">
-        <v>-440.3549634</v>
+        <v>-448.31692725</v>
       </c>
       <c r="Q86">
-        <v>-321.1549634</v>
+        <v>-329.1169272500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2785827173982071</v>
+        <v>0.2941015652247543</v>
       </c>
       <c r="T86">
-        <v>4.665817636105881</v>
+        <v>4.976872145179605</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08539485070454249</v>
+        <v>0.0843902054021361</v>
       </c>
       <c r="W86">
-        <v>0.2156638942038689</v>
+        <v>0.2159007895661763</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3415794028181699</v>
+        <v>0.3375608216085444</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.227630905914963</v>
+        <v>0.229530905914963</v>
       </c>
       <c r="C87">
-        <v>-1815.52096092621</v>
+        <v>-1867.43400594136</v>
       </c>
       <c r="D87">
-        <v>666.4640390737903</v>
+        <v>659.5719940586404</v>
       </c>
       <c r="E87">
-        <v>3237.985000000001</v>
+        <v>3283.006</v>
       </c>
       <c r="F87">
-        <v>3826.785</v>
+        <v>3871.806</v>
       </c>
       <c r="G87">
         <v>1344.8</v>
@@ -8415,37 +8415,37 @@
         <v>304.6</v>
       </c>
       <c r="M87">
-        <v>902.3559030000001</v>
+        <v>912.9718548000001</v>
       </c>
       <c r="N87">
-        <v>-597.7559030000001</v>
+        <v>-608.3718548000001</v>
       </c>
       <c r="O87">
-        <v>-149.43897575</v>
+        <v>-152.0929637</v>
       </c>
       <c r="P87">
-        <v>-448.31692725</v>
+        <v>-456.2788911</v>
       </c>
       <c r="Q87">
-        <v>-329.1169272500001</v>
+        <v>-337.0788911</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2941015652247543</v>
+        <v>0.3118373913122368</v>
       </c>
       <c r="T87">
-        <v>4.976872145179605</v>
+        <v>5.332363012692436</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0843902054021361</v>
+        <v>0.08340892394397173</v>
       </c>
       <c r="W87">
-        <v>0.2159007895661763</v>
+        <v>0.2161321757340115</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3375608216085444</v>
+        <v>0.3336356957758869</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.229530905914963</v>
+        <v>0.231430905914963</v>
       </c>
       <c r="C88">
-        <v>-1867.43400594136</v>
+        <v>-1919.205965769598</v>
       </c>
       <c r="D88">
-        <v>659.5719940586404</v>
+        <v>652.821034230402</v>
       </c>
       <c r="E88">
-        <v>3283.006</v>
+        <v>3328.027</v>
       </c>
       <c r="F88">
-        <v>3871.806</v>
+        <v>3916.827</v>
       </c>
       <c r="G88">
         <v>1344.8</v>
@@ -8497,37 +8497,37 @@
         <v>304.6</v>
       </c>
       <c r="M88">
-        <v>912.9718548000001</v>
+        <v>923.5878066000001</v>
       </c>
       <c r="N88">
-        <v>-608.3718548000001</v>
+        <v>-618.9878066000001</v>
       </c>
       <c r="O88">
-        <v>-152.0929637</v>
+        <v>-154.74695165</v>
       </c>
       <c r="P88">
-        <v>-456.2788911</v>
+        <v>-464.2408549500001</v>
       </c>
       <c r="Q88">
-        <v>-337.0788911</v>
+        <v>-345.0408549500001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3118373913122368</v>
+        <v>0.3323018060285627</v>
       </c>
       <c r="T88">
-        <v>5.332363012692436</v>
+        <v>5.742544782899546</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08340892394397173</v>
+        <v>0.08245020068024791</v>
       </c>
       <c r="W88">
-        <v>0.2161321757340115</v>
+        <v>0.2163582426795976</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3336356957758869</v>
+        <v>0.3298008027209917</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.231430905914963</v>
+        <v>0.233330905914963</v>
       </c>
       <c r="C89">
-        <v>-1919.205965769598</v>
+        <v>-1970.841128693763</v>
       </c>
       <c r="D89">
-        <v>652.821034230402</v>
+        <v>646.2068713062372</v>
       </c>
       <c r="E89">
-        <v>3328.027</v>
+        <v>3373.048000000001</v>
       </c>
       <c r="F89">
-        <v>3916.827</v>
+        <v>3961.848</v>
       </c>
       <c r="G89">
         <v>1344.8</v>
@@ -8579,37 +8579,37 @@
         <v>304.6</v>
       </c>
       <c r="M89">
-        <v>923.5878066000001</v>
+        <v>934.2037584000001</v>
       </c>
       <c r="N89">
-        <v>-618.9878066000001</v>
+        <v>-629.6037584000001</v>
       </c>
       <c r="O89">
-        <v>-154.74695165</v>
+        <v>-157.4009396</v>
       </c>
       <c r="P89">
-        <v>-464.2408549500001</v>
+        <v>-472.2028188</v>
       </c>
       <c r="Q89">
-        <v>-345.0408549500001</v>
+        <v>-353.0028188000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3323018060285627</v>
+        <v>0.3561769565309429</v>
       </c>
       <c r="T89">
-        <v>5.742544782899546</v>
+        <v>6.221090181474509</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08245020068024791</v>
+        <v>0.08151326658160873</v>
       </c>
       <c r="W89">
-        <v>0.2163582426795976</v>
+        <v>0.2165791717400567</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3298008027209917</v>
+        <v>0.3260530663264349</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.233330905914963</v>
+        <v>0.235230905914963</v>
       </c>
       <c r="C90">
-        <v>-1970.841128693763</v>
+        <v>-2022.343610950059</v>
       </c>
       <c r="D90">
-        <v>646.2068713062372</v>
+        <v>639.7253890499417</v>
       </c>
       <c r="E90">
-        <v>3373.048000000001</v>
+        <v>3418.069</v>
       </c>
       <c r="F90">
-        <v>3961.848</v>
+        <v>4006.869000000001</v>
       </c>
       <c r="G90">
         <v>1344.8</v>
@@ -8661,37 +8661,37 @@
         <v>304.6</v>
       </c>
       <c r="M90">
-        <v>934.2037584000001</v>
+        <v>944.8197102000001</v>
       </c>
       <c r="N90">
-        <v>-629.6037584000001</v>
+        <v>-640.2197102000001</v>
       </c>
       <c r="O90">
-        <v>-157.4009396</v>
+        <v>-160.05492755</v>
       </c>
       <c r="P90">
-        <v>-472.2028188</v>
+        <v>-480.1647826500001</v>
       </c>
       <c r="Q90">
-        <v>-353.0028188000001</v>
+        <v>-360.9647826500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3561769565309429</v>
+        <v>0.3843930434883014</v>
       </c>
       <c r="T90">
-        <v>6.221090181474509</v>
+        <v>6.786643834335828</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08151326658160873</v>
+        <v>0.08059738718181537</v>
       </c>
       <c r="W90">
-        <v>0.2165791717400567</v>
+        <v>0.2167951361025279</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3260530663264349</v>
+        <v>0.3223895487272614</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.235230905914963</v>
+        <v>0.237130905914963</v>
       </c>
       <c r="C91">
-        <v>-2022.343610950059</v>
+        <v>-2073.717365270551</v>
       </c>
       <c r="D91">
-        <v>639.7253890499417</v>
+        <v>633.3726347294498</v>
       </c>
       <c r="E91">
-        <v>3418.069</v>
+        <v>3463.09</v>
       </c>
       <c r="F91">
-        <v>4006.869000000001</v>
+        <v>4051.89</v>
       </c>
       <c r="G91">
         <v>1344.8</v>
@@ -8743,37 +8743,37 @@
         <v>304.6</v>
       </c>
       <c r="M91">
-        <v>944.8197102000001</v>
+        <v>955.4356620000001</v>
       </c>
       <c r="N91">
-        <v>-640.2197102000001</v>
+        <v>-650.8356620000001</v>
       </c>
       <c r="O91">
-        <v>-160.05492755</v>
+        <v>-162.7089155</v>
       </c>
       <c r="P91">
-        <v>-480.1647826500001</v>
+        <v>-488.1267465000001</v>
       </c>
       <c r="Q91">
-        <v>-360.9647826500001</v>
+        <v>-368.9267465000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3843930434883014</v>
+        <v>0.4182523478371316</v>
       </c>
       <c r="T91">
-        <v>6.786643834335828</v>
+        <v>7.465308217769411</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08059738718181537</v>
+        <v>0.07970186065757298</v>
       </c>
       <c r="W91">
-        <v>0.2167951361025279</v>
+        <v>0.2170063012569443</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3223895487272614</v>
+        <v>0.3188074426302919</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.237130905914963</v>
+        <v>0.239030905914963</v>
       </c>
       <c r="C92">
-        <v>-2073.717365270551</v>
+        <v>-2124.966188921678</v>
       </c>
       <c r="D92">
-        <v>633.3726347294498</v>
+        <v>627.1448110783224</v>
       </c>
       <c r="E92">
-        <v>3463.09</v>
+        <v>3508.111</v>
       </c>
       <c r="F92">
-        <v>4051.89</v>
+        <v>4096.911</v>
       </c>
       <c r="G92">
         <v>1344.8</v>
@@ -8825,37 +8825,37 @@
         <v>304.6</v>
       </c>
       <c r="M92">
-        <v>955.4356620000001</v>
+        <v>966.0516138</v>
       </c>
       <c r="N92">
-        <v>-650.8356620000001</v>
+        <v>-661.4516138</v>
       </c>
       <c r="O92">
-        <v>-162.7089155</v>
+        <v>-165.36290345</v>
       </c>
       <c r="P92">
-        <v>-488.1267465000001</v>
+        <v>-496.08871035</v>
       </c>
       <c r="Q92">
-        <v>-368.9267465000001</v>
+        <v>-376.8887103500001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4182523478371316</v>
+        <v>0.4596359420412574</v>
       </c>
       <c r="T92">
-        <v>7.465308217769411</v>
+        <v>8.29478690863268</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07970186065757298</v>
+        <v>0.0788260160349623</v>
       </c>
       <c r="W92">
-        <v>0.2170063012569443</v>
+        <v>0.2172128254189559</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3188074426302919</v>
+        <v>0.3153040641398491</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.239030905914963</v>
+        <v>0.240930905914963</v>
       </c>
       <c r="C93">
-        <v>-2124.966188921678</v>
+        <v>-2176.09373127314</v>
       </c>
       <c r="D93">
-        <v>627.1448110783224</v>
+        <v>621.038268726861</v>
       </c>
       <c r="E93">
-        <v>3508.111</v>
+        <v>3553.132000000001</v>
       </c>
       <c r="F93">
-        <v>4096.911</v>
+        <v>4141.932000000001</v>
       </c>
       <c r="G93">
         <v>1344.8</v>
@@ -8907,37 +8907,37 @@
         <v>304.6</v>
       </c>
       <c r="M93">
-        <v>966.0516138</v>
+        <v>976.6675656000002</v>
       </c>
       <c r="N93">
-        <v>-661.4516138</v>
+        <v>-672.0675656000002</v>
       </c>
       <c r="O93">
-        <v>-165.36290345</v>
+        <v>-168.0168914</v>
       </c>
       <c r="P93">
-        <v>-496.08871035</v>
+        <v>-504.0506742000001</v>
       </c>
       <c r="Q93">
-        <v>-376.8887103500001</v>
+        <v>-384.8506742000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4596359420412574</v>
+        <v>0.5113654347964146</v>
       </c>
       <c r="T93">
-        <v>8.29478690863268</v>
+        <v>9.331635272211768</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0788260160349623</v>
+        <v>0.07796921151284313</v>
       </c>
       <c r="W93">
-        <v>0.2172128254189559</v>
+        <v>0.2174148599252716</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3153040641398491</v>
+        <v>0.3118768460513726</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.240930905914963</v>
+        <v>0.242830905914963</v>
       </c>
       <c r="C94">
-        <v>-2176.09373127314</v>
+        <v>-2227.103500928852</v>
       </c>
       <c r="D94">
-        <v>621.038268726861</v>
+        <v>615.0494990711485</v>
       </c>
       <c r="E94">
-        <v>3553.132000000001</v>
+        <v>3598.153</v>
       </c>
       <c r="F94">
-        <v>4141.932000000001</v>
+        <v>4186.953</v>
       </c>
       <c r="G94">
         <v>1344.8</v>
@@ -8989,37 +8989,37 @@
         <v>304.6</v>
       </c>
       <c r="M94">
-        <v>976.6675656000002</v>
+        <v>987.2835174000002</v>
       </c>
       <c r="N94">
-        <v>-672.0675656000002</v>
+        <v>-682.6835174000001</v>
       </c>
       <c r="O94">
-        <v>-168.0168914</v>
+        <v>-170.67087935</v>
       </c>
       <c r="P94">
-        <v>-504.0506742000001</v>
+        <v>-512.0126380500001</v>
       </c>
       <c r="Q94">
-        <v>-384.8506742000001</v>
+        <v>-392.8126380500001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5113654347964146</v>
+        <v>0.5778747826244739</v>
       </c>
       <c r="T94">
-        <v>9.331635272211768</v>
+        <v>10.66472602538488</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07796921151284313</v>
+        <v>0.07713083289442546</v>
       </c>
       <c r="W94">
-        <v>0.2174148599252716</v>
+        <v>0.2176125496034945</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3118768460513726</v>
+        <v>0.3085233315777018</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.242830905914963</v>
+        <v>0.244730905914963</v>
       </c>
       <c r="C95">
-        <v>-2227.103500928852</v>
+        <v>-2277.998872449256</v>
       </c>
       <c r="D95">
-        <v>615.0494990711485</v>
+        <v>609.1751275507439</v>
       </c>
       <c r="E95">
-        <v>3598.153</v>
+        <v>3643.174</v>
       </c>
       <c r="F95">
-        <v>4186.953</v>
+        <v>4231.974</v>
       </c>
       <c r="G95">
         <v>1344.8</v>
@@ -9071,37 +9071,37 @@
         <v>304.6</v>
       </c>
       <c r="M95">
-        <v>987.2835174000002</v>
+        <v>997.8994692000001</v>
       </c>
       <c r="N95">
-        <v>-682.6835174000001</v>
+        <v>-693.2994692000001</v>
       </c>
       <c r="O95">
-        <v>-170.67087935</v>
+        <v>-173.3248673</v>
       </c>
       <c r="P95">
-        <v>-512.0126380500001</v>
+        <v>-519.9746019</v>
       </c>
       <c r="Q95">
-        <v>-392.8126380500001</v>
+        <v>-400.7746019000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5778747826244739</v>
+        <v>0.6665539130618863</v>
       </c>
       <c r="T95">
-        <v>10.66472602538488</v>
+        <v>12.44218036294903</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07713083289442546</v>
+        <v>0.07631029211895285</v>
       </c>
       <c r="W95">
-        <v>0.2176125496034945</v>
+        <v>0.2178060331183509</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3085233315777018</v>
+        <v>0.3052411684758114</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.244730905914963</v>
+        <v>0.246630905914963</v>
       </c>
       <c r="C96">
-        <v>-2277.998872449256</v>
+        <v>-2328.783092692044</v>
       </c>
       <c r="D96">
-        <v>609.1751275507439</v>
+        <v>603.4119073079565</v>
       </c>
       <c r="E96">
-        <v>3643.174</v>
+        <v>3688.195000000001</v>
       </c>
       <c r="F96">
-        <v>4231.974</v>
+        <v>4276.995000000001</v>
       </c>
       <c r="G96">
         <v>1344.8</v>
@@ -9153,37 +9153,37 @@
         <v>304.6</v>
       </c>
       <c r="M96">
-        <v>997.8994692000001</v>
+        <v>1008.515421</v>
       </c>
       <c r="N96">
-        <v>-693.2994692000001</v>
+        <v>-703.9154210000002</v>
       </c>
       <c r="O96">
-        <v>-173.3248673</v>
+        <v>-175.97885525</v>
       </c>
       <c r="P96">
-        <v>-519.9746019</v>
+        <v>-527.9365657500001</v>
       </c>
       <c r="Q96">
-        <v>-400.7746019000001</v>
+        <v>-408.7365657500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6665539130618863</v>
+        <v>0.7907046956742639</v>
       </c>
       <c r="T96">
-        <v>12.44218036294903</v>
+        <v>14.93061643553884</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07631029211895285</v>
+        <v>0.07550702588612176</v>
       </c>
       <c r="W96">
-        <v>0.2178060331183509</v>
+        <v>0.2179954432960525</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3052411684758114</v>
+        <v>0.3020281035444871</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.246630905914963</v>
+        <v>0.248530905914963</v>
       </c>
       <c r="C97">
-        <v>-2328.783092692044</v>
+        <v>-2379.459286796321</v>
       </c>
       <c r="D97">
-        <v>603.4119073079565</v>
+        <v>597.7567132036793</v>
       </c>
       <c r="E97">
-        <v>3688.195000000001</v>
+        <v>3733.216</v>
       </c>
       <c r="F97">
-        <v>4276.995000000001</v>
+        <v>4322.016000000001</v>
       </c>
       <c r="G97">
         <v>1344.8</v>
@@ -9235,37 +9235,37 @@
         <v>304.6</v>
       </c>
       <c r="M97">
-        <v>1008.515421</v>
+        <v>1019.1313728</v>
       </c>
       <c r="N97">
-        <v>-703.9154210000002</v>
+        <v>-714.5313728000001</v>
       </c>
       <c r="O97">
-        <v>-175.97885525</v>
+        <v>-178.6328432</v>
       </c>
       <c r="P97">
-        <v>-527.9365657500001</v>
+        <v>-535.8985296000001</v>
       </c>
       <c r="Q97">
-        <v>-408.7365657500001</v>
+        <v>-416.6985296000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7907046956742639</v>
+        <v>0.9769308695928303</v>
       </c>
       <c r="T97">
-        <v>14.93061643553884</v>
+        <v>18.66327054442356</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07550702588612176</v>
+        <v>0.07472049436647467</v>
       </c>
       <c r="W97">
-        <v>0.2179954432960525</v>
+        <v>0.2181809074283853</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3020281035444871</v>
+        <v>0.2988819774658987</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.248530905914963</v>
+        <v>0.250430905914963</v>
       </c>
       <c r="C98">
-        <v>-2379.459286796321</v>
+        <v>-2430.030463833406</v>
       </c>
       <c r="D98">
-        <v>597.7567132036793</v>
+        <v>592.2065361665948</v>
       </c>
       <c r="E98">
-        <v>3733.216</v>
+        <v>3778.237</v>
       </c>
       <c r="F98">
-        <v>4322.016000000001</v>
+        <v>4367.037</v>
       </c>
       <c r="G98">
         <v>1344.8</v>
@@ -9317,37 +9317,37 @@
         <v>304.6</v>
       </c>
       <c r="M98">
-        <v>1019.1313728</v>
+        <v>1029.7473246</v>
       </c>
       <c r="N98">
-        <v>-714.5313728000001</v>
+        <v>-725.1473246000002</v>
       </c>
       <c r="O98">
-        <v>-178.6328432</v>
+        <v>-181.28683115</v>
       </c>
       <c r="P98">
-        <v>-535.8985296000001</v>
+        <v>-543.8604934500001</v>
       </c>
       <c r="Q98">
-        <v>-416.6985296000001</v>
+        <v>-424.6604934500002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.976930869592828</v>
+        <v>1.287307826123771</v>
       </c>
       <c r="T98">
-        <v>18.66327054442351</v>
+        <v>24.88436072589802</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07472049436647467</v>
+        <v>0.07395017999156256</v>
       </c>
       <c r="W98">
-        <v>0.2181809074283853</v>
+        <v>0.2183625475579896</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2988819774658987</v>
+        <v>0.2958007199662502</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.250430905914963</v>
+        <v>0.252330905914963</v>
       </c>
       <c r="C99">
-        <v>-2430.030463833406</v>
+        <v>-2480.499522145703</v>
       </c>
       <c r="D99">
-        <v>592.2065361665948</v>
+        <v>586.7584778542965</v>
       </c>
       <c r="E99">
-        <v>3778.237</v>
+        <v>3823.258</v>
       </c>
       <c r="F99">
-        <v>4367.037</v>
+        <v>4412.058</v>
       </c>
       <c r="G99">
         <v>1344.8</v>
@@ -9399,37 +9399,37 @@
         <v>304.6</v>
       </c>
       <c r="M99">
-        <v>1029.7473246</v>
+        <v>1040.3632764</v>
       </c>
       <c r="N99">
-        <v>-725.1473246000002</v>
+        <v>-735.7632764000001</v>
       </c>
       <c r="O99">
-        <v>-181.28683115</v>
+        <v>-183.9408191</v>
       </c>
       <c r="P99">
-        <v>-543.8604934500001</v>
+        <v>-551.8224573000001</v>
       </c>
       <c r="Q99">
-        <v>-424.6604934500002</v>
+        <v>-432.6224573000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.287307826123771</v>
+        <v>1.908061739185656</v>
       </c>
       <c r="T99">
-        <v>24.88436072589802</v>
+        <v>37.32654108884702</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07395017999156256</v>
+        <v>0.07319558631817927</v>
       </c>
       <c r="W99">
-        <v>0.2183625475579896</v>
+        <v>0.2185404807461734</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2958007199662502</v>
+        <v>0.2927823452727171</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.252330905914963</v>
+        <v>0.254230905914963</v>
       </c>
       <c r="C100">
-        <v>-2480.499522145703</v>
+        <v>-2530.869254393589</v>
       </c>
       <c r="D100">
-        <v>586.7584778542965</v>
+        <v>581.409745606412</v>
       </c>
       <c r="E100">
-        <v>3823.258</v>
+        <v>3868.279</v>
       </c>
       <c r="F100">
-        <v>4412.058</v>
+        <v>4457.079000000001</v>
       </c>
       <c r="G100">
         <v>1344.8</v>
@@ -9481,37 +9481,37 @@
         <v>304.6</v>
       </c>
       <c r="M100">
-        <v>1040.3632764</v>
+        <v>1050.9792282</v>
       </c>
       <c r="N100">
-        <v>-735.7632764000001</v>
+        <v>-746.3792282000001</v>
       </c>
       <c r="O100">
-        <v>-183.9408191</v>
+        <v>-186.59480705</v>
       </c>
       <c r="P100">
-        <v>-551.8224573000001</v>
+        <v>-559.7844211500001</v>
       </c>
       <c r="Q100">
-        <v>-432.6224573000001</v>
+        <v>-440.5844211500001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.908061739185656</v>
+        <v>3.770323478371311</v>
       </c>
       <c r="T100">
-        <v>37.32654108884702</v>
+        <v>74.65308217769403</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07319558631817927</v>
+        <v>0.07245623696142998</v>
       </c>
       <c r="W100">
-        <v>0.2185404807461734</v>
+        <v>0.2187148193244948</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2927823452727171</v>
+        <v>0.28982494784572</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.254230905914963</v>
-      </c>
-      <c r="C101">
-        <v>-2530.869254393589</v>
-      </c>
-      <c r="D101">
-        <v>581.409745606412</v>
-      </c>
-      <c r="E101">
-        <v>3868.279</v>
-      </c>
-      <c r="F101">
-        <v>4457.079000000001</v>
-      </c>
-      <c r="G101">
-        <v>1344.8</v>
-      </c>
-      <c r="H101">
-        <v>3913.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>423.8</v>
-      </c>
-      <c r="K101">
-        <v>119.2</v>
-      </c>
-      <c r="L101">
-        <v>304.6</v>
-      </c>
-      <c r="M101">
-        <v>1050.9792282</v>
-      </c>
-      <c r="N101">
-        <v>-746.3792282000001</v>
-      </c>
-      <c r="O101">
-        <v>-186.59480705</v>
-      </c>
-      <c r="P101">
-        <v>-559.7844211500001</v>
-      </c>
-      <c r="Q101">
-        <v>-440.5844211500001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.770323478371311</v>
-      </c>
-      <c r="T101">
-        <v>74.65308217769403</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07245623696142998</v>
-      </c>
-      <c r="W101">
-        <v>0.2187148193244948</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.28982494784572</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
